--- a/eval/nbfc_retrieval_test_questions_results.xlsx
+++ b/eval/nbfc_retrieval_test_questions_results.xlsx
@@ -511,12 +511,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>The asset-size threshold for a non-deposit-taking NBFC to be placed in the Middle Layer is ₹1,000 crore and above [1]. This applies to non-deposit taking NBFCs with asset size of ₹1,000 crore and above, as explicitly stated in the Middle Layer composition [1], and reinforced by criteria for NBFC-ML status [3].</t>
+          <t>The asset-size threshold for a non-deposit-taking NBFC to be placed in the Middle Layer is ₹1,000 crore. This is explicitly stated in [1], which includes non-deposit taking NBFCs with asset size of ₹1,000 crore and above in the Middle Layer. Additionally, [2] confirms that once an NBFC reaches ₹1,000 crore, it is subject to Middle Layer regulations. [3] further supports this by noting that existing NBFC-ND-SI with asset size ₹500 crore and above but below ₹1,000 crore are classified as Base Layer, implying ₹1,000 crore as the threshold for Middle Layer.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.10 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.11 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.12 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13 | 13590_SUP-Fraud-Risk-Management.pdf p.4</t>
+          <t>12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.10 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.11 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.12 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13 | 13592_SUP-Cybersecurity-Technology-Risk-Resilience.pdf p.3</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -564,12 +564,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>The minimum CRAR for a Middle Layer NBFC is 15% of aggregate RWAs [1]. The Tier 1 capital requirement is 10% of aggregate RWAs [1], with Tier 2 capital not exceeding 100% of Tier 1 capital. Thus, Tier 1 constitutes 10% of the CRAR.</t>
+          <t>The minimum CRAR for a Middle Layer NBFC is 15 per cent of the aggregate RWAs [1]. Of this, the minimum Tier 1 capital required is 10 per cent of the aggregate RWAs [1].</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12959_Prudential-Norms-on-Capital-Adequacy.pdf p.7 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.7 | 13586_SUP-Miscellaneous.pdf p.8 | 12933_Microfinance-Institution.pdf p.9 | 12938_Standalone-Primary-Dealers.pdf p.9 | 12938_Standalone-Primary-Dealers.pdf p.68</t>
+          <t>12959_Prudential-Norms-on-Capital-Adequacy.pdf p.7 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.7 | 13586_SUP-Miscellaneous.pdf p.8 | 12933_Microfinance-Institution.pdf p.9 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.13 | 12938_Standalone-Primary-Dealers.pdf p.9</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>9.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -617,12 +617,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>The Common Equity Tier 1 (CET1) ratio for an Upper Layer NBFC must be at least 9 per cent of the aggregate Risk Weighted Assets (RWAs) [1].</t>
+          <t>An NBFC - Upper Layer (NBFC - UL (Upper Layer)) shall maintain a minimum Common Equity Tier 1 (CET1) capital of 9 per cent of the aggregate RWAs [1].</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>12959_Prudential-Norms-on-Capital-Adequacy.pdf p.7 | 12933_Microfinance-Institution.pdf p.9 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.7 | 12944_Declaration-of-Dividends.pdf p.6 | 12953_Concentration-Risk-Management.pdf p.10 | 12957_Credit-Facilities.pdf p.47</t>
+          <t>12959_Prudential-Norms-on-Capital-Adequacy.pdf p.7 | 12953_Concentration-Risk-Management.pdf p.10 | 12933_Microfinance-Institution.pdf p.9 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.7 | 12944_Declaration-of-Dividends.pdf p.6 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.22</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -670,12 +670,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>The minimum Net Owned Fund (NOF) required for an NBFC-ICC is ₹10 crore, which must be achieved by March 31, 2027 [1]. Existing NBFC-ICC currently have a NOF of ₹2 crore and must reach ₹5 crore by March 31, 2025, and ₹10 crore by March 31, 2027 [1].</t>
+          <t>The minimum Net Owned Fund (NOF) required for an NBFC-ICC is ₹10 crore, which must be achieved by March 31, 2027 [2]. Existing NBFC-ICC entities currently have a NOF of ₹2 crore and must progressively increase it to ₹5 crore by March 31, 2025, and ₹10 crore by March 31, 2027 [2].</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.21 | 12939_Housing-Finance-Companies.pdf p.13 | 12936_Account-Aggregator.pdf p.8 | 12934_Peer-to-Peer-Lending-Platform.pdf p.5 | 12939_Housing-Finance-Companies.pdf p.8 | 12961_Undertaking-of-Financial-Services.pdf p.13</t>
+          <t>12939_Housing-Finance-Companies.pdf p.13 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.21 | 12936_Account-Aggregator.pdf p.8 | 12934_Peer-to-Peer-Lending-Platform.pdf p.5 | 12939_Housing-Finance-Companies.pdf p.8 | 12961_Undertaking-of-Financial-Services.pdf p.13</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9.4</v>
+        <v>10.4</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -723,12 +723,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>The minimum NOF for NBFC-P2P is ₹2 crore [1], and for NBFC-AA, it is also ₹2 crore [1].</t>
+          <t>The minimum NOF for NBFC-P2P is ₹2 crore [1] and for NBFC-AA is also ₹2 crore [1].</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.21 | 12961_Undertaking-of-Financial-Services.pdf p.25 | 12931_Miscellaneous.pdf p.17 | 12939_Housing-Finance-Companies.pdf p.13 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.10 | 12934_Peer-to-Peer-Lending-Platform.pdf p.10</t>
+          <t>12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.21 | 12961_Undertaking-of-Financial-Services.pdf p.25 | 12931_Miscellaneous.pdf p.17 | 12934_Peer-to-Peer-Lending-Platform.pdf p.10 | 12939_Housing-Finance-Companies.pdf p.13 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.2</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -776,12 +776,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>After the glide path ended (March 31, 2026), the NPA classification for a Base Layer NBFC is triggered by an overdue period of **more than 90 days** [1]. This applies to NBFCs transitioning to the 90-day NPA norm as per the glide path timeline.</t>
+          <t>After the glide path ended (March 31, 2026), the NPA classification for NBFCs follows the 90-day overdue threshold. This is specified in the glide path timeline for applicable NBFCs [1], which transitions them to the 90-day norm upon completion of the glide path. For Base Layer NBFCs, the NPA classification is triggered by an overdue period of **more than 90 days** [1].</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.17 | 12931_Miscellaneous.pdf p.14 | 12947_Resolution-of-Stressed-Assets.pdf p.15 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.7 | 12951_Securitisation-Transactions.pdf p.46 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.20</t>
+          <t>12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.17 | 12931_Miscellaneous.pdf p.14 | 12947_Resolution-of-Stressed-Assets.pdf p.15 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.7 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.20 | 12949_Asset-Liability-Management.pdf p.29</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9.800000000000001</v>
+        <v>14.2</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -829,12 +829,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>The provisioning requirement for sub-standard assets is 10% of the total outstanding, as specified in [6] (section 32(1)). For Housing Finance Companies (HFCs), sub-standard assets require a general provision of 15% of the total outstanding [3]. Additionally, for mortgage guarantee assets classified as sub-standard, a general provision of 10% of the total outstanding is mandated [5].</t>
+          <t>The provisioning requirement for sub-standard assets is a general provision of **10 per cent of total outstanding** [4], and this rate is also explicitly stated in the provisioning norms for NPAs under paragraph 32(1) of the 2025 Directions [5].</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.18 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.10 | 12939_Housing-Finance-Companies.pdf p.26 | 12939_Housing-Finance-Companies.pdf p.25 | 12935_Mortgage-Guarantee-Companies.pdf p.22 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.10</t>
+          <t>12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.18 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.10 | 12939_Housing-Finance-Companies.pdf p.25 | 12935_Mortgage-Guarantee-Companies.pdf p.22 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.10 | 12937_Core-Investment-Companies.pdf p.19</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>10.6</v>
+        <v>7.7</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -882,12 +882,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>The standard asset provisioning rate for Middle Layer NBFCs is 0.40 per cent of the outstanding, as specified in paragraph 55 [1], which applies to NBFC-ML. This rate is also referenced in passage [5] for Middle Layer CICs.</t>
+          <t>The standard asset provisioning rate for Middle Layer NBFCs (NBFC-ML) is 0.40 per cent of the outstanding amount, as specified in paragraph 55 of the RBI directions [1]. This rate also applies to microfinance loans [1].</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.21 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.22 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.18 | 12933_Microfinance-Institution.pdf p.10 | 12937_Core-Investment-Companies.pdf p.19 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.10</t>
+          <t>12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.21 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.22 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.18 | 12933_Microfinance-Institution.pdf p.10 | 12937_Core-Investment-Companies.pdf p.19 | 12947_Resolution-of-Stressed-Assets.pdf p.15</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -935,26 +935,26 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The NBFC must periodically update KYC for high-risk customers every 2 years, medium-risk customers every 8 years, and low-risk customers every 10 years from the date of account opening or last KYC updation [1].</t>
+          <t>High-risk customers require periodic KYC updation at least once every two years, medium-risk customers once every eight years, and low-risk customers once every 10 years [1].</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>12943_Know-Your-Customer.pdf p.41 | 12943_Know-Your-Customer.pdf p.56 | 12943_Know-Your-Customer.pdf p.42 | 12943_Know-Your-Customer.pdf p.44 | 12943_Know-Your-Customer.pdf p.34 | 12943_Know-Your-Customer.pdf p.15</t>
+          <t>12943_Know-Your-Customer.pdf p.41 | 12943_Know-Your-Customer.pdf p.57 | 12943_Know-Your-Customer.pdf p.42 | 12943_Know-Your-Customer.pdf p.44 | 12943_Know-Your-Customer.pdf p.34 | 12943_Know-Your-Customer.pdf p.15</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>all key figures present (2years, 8years, 10years)</t>
+          <t>found 10years; missing 2years, 8years</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -988,12 +988,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Customer identification records must be preserved for at least five years after the business relationship has ended [1](47.2). Transaction records must be maintained for at least five years from the date of the transaction [1](47.1).</t>
+          <t>Customer identification and transaction records must be preserved for at least five years from the date of the transaction [1], and records pertaining to customer identification (including addresses) must be preserved for five years after the business relationship has ended [1]. For non-profit organization customers, registration details must be maintained for five years after the business relationship ends or the account is closed, whichever is later [1].</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>12943_Know-Your-Customer.pdf p.48 | 12943_Know-Your-Customer.pdf p.34 | 12943_Know-Your-Customer.pdf p.44 | 12943_Know-Your-Customer.pdf p.22 | 12957_Credit-Facilities.pdf p.20 | 12943_Know-Your-Customer.pdf p.41</t>
+          <t>12943_Know-Your-Customer.pdf p.48 | 12943_Know-Your-Customer.pdf p.34 | 12943_Know-Your-Customer.pdf p.44 | 12943_Know-Your-Customer.pdf p.22 | 12943_Know-Your-Customer.pdf p.57 | 12957_Credit-Facilities.pdf p.20</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>The context passages do not specify an exact timeline for filing a Suspicious Transaction Report (STR) with FIU-IND. However, they mention that delays in reporting a transaction or rectifying a mis-represented transaction constitute separate violations [1]. Specific time limits for filing STRs are not provided in the cited texts.</t>
+          <t>The context passages do not specify a particular timeline for filing Suspicious Transaction Reports (STRs) with FIU-IND. While passage [1] mentions that delays in reporting constitute violations [1], it does not define the exact time limit. Other sections reference reporting obligations but do not explicitly state a timeframe for STR filings.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>12943_Know-Your-Customer.pdf p.50 | 12943_Know-Your-Customer.pdf p.73 | 12943_Know-Your-Customer.pdf p.63 | 12941_Managing-Risks-in-Outsourcing.pdf p.13 | 12939_Housing-Finance-Companies.pdf p.83 | 12943_Know-Your-Customer.pdf p.60</t>
+          <t>12943_Know-Your-Customer.pdf p.50 | 12943_Know-Your-Customer.pdf p.72 | 12943_Know-Your-Customer.pdf p.63 | 12941_Managing-Risks-in-Outsourcing.pdf p.13 | 12939_Housing-Finance-Companies.pdf p.83 | 12943_Know-Your-Customer.pdf p.60</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>9.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>12958_Acceptance-of-Public-Deposits.pdf p.13 | 12931_Miscellaneous.pdf p.6 | 12958_Acceptance-of-Public-Deposits.pdf p.13 | 12958_Acceptance-of-Public-Deposits.pdf p.13 | 12958_Acceptance-of-Public-Deposits.pdf p.18 | 12958_Acceptance-of-Public-Deposits.pdf p.22</t>
+          <t>12958_Acceptance-of-Public-Deposits.pdf p.13 | 12931_Miscellaneous.pdf p.5 | 12958_Acceptance-of-Public-Deposits.pdf p.13 | 12958_Acceptance-of-Public-Deposits.pdf p.13 | 12958_Acceptance-of-Public-Deposits.pdf p.18 | 12958_Acceptance-of-Public-Deposits.pdf p.22</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>The ceiling on public deposits an NBFC-D can hold relative to its NOF is **one and one-half times** its NOF. This is specified in [1], which states that an NBFC shall not accept or renew public deposits exceeding 1.5 times its NOF, with exceptions for matured deposits requiring depositor consent.</t>
+          <t>The ceiling on public deposits an NBFC-D can hold relative to its NOF is **one and one-half times** its NOF [1].</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1157,16 +1157,16 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>all key figures present (1.5times)</t>
+          <t>none of the expected figures appear (1.5times)</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>An NBFC-D must maintain **15 per cent** of the 'public deposit' outstanding in liquid assets, specifically invested in unencumbered approved securities valued at not exceeding the current market price [1]. This requirement is outlined in paragraph 10 of Chapter-II of the Directions.</t>
+          <t>The percentage of public deposits that an NBFC-D must maintain in liquid assets is **15%**. This is specified in paragraph 10 of Chapter-II of the Directions, which requires NBFC-Ds to invest in unencumbered approved securities valued at not less than 15% of the public deposits outstanding [1].</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>12958_Acceptance-of-Public-Deposits.pdf p.12 | 12949_Asset-Liability-Management.pdf p.17 | 12939_Housing-Finance-Companies.pdf p.8 | 12949_Asset-Liability-Management.pdf p.20 | 12958_Acceptance-of-Public-Deposits.pdf p.2 | 12939_Housing-Finance-Companies.pdf p.38</t>
+          <t>12958_Acceptance-of-Public-Deposits.pdf p.12 | 12939_Housing-Finance-Companies.pdf p.8 | 12949_Asset-Liability-Management.pdf p.20 | 12958_Acceptance-of-Public-Deposits.pdf p.2 | 12939_Housing-Finance-Companies.pdf p.38 | 12958_Acceptance-of-Public-Deposits.pdf p.26</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -1253,26 +1253,26 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>The NBFC must compensate the borrower at the rate of ₹5,000 for each day of delay beyond the 30-day period specified in paragraph 39 of [1] and paragraph 69 of [2]. This applies if the delay is attributable to the NBFC in returning original movable/immovable property documents or pledged collateral after full repayment.</t>
+          <t>The NBFC must compensate the borrower at the rate of ₹5,000 for each day of delay beyond 30 days in releasing original movable/immovable property documents, if the delay is attributable to the NBFC [1]. Additionally, if the delay is not attributable to the NBFC, the NBFC must communicate the reasons for the delay to the borrower [2]. The 30-day timeline for release is specified in F.1 [3].</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>12942_Responsible-Business-Conduct.pdf p.20 | 12942_Responsible-Business-Conduct.pdf p.24 | 12942_Responsible-Business-Conduct.pdf p.19 | 12957_Credit-Facilities.pdf p.15 | 12942_Responsible-Business-Conduct.pdf p.14 | 12947_Resolution-of-Stressed-Assets.pdf p.31</t>
+          <t>12942_Responsible-Business-Conduct.pdf p.20 | 12942_Responsible-Business-Conduct.pdf p.24 | 12942_Responsible-Business-Conduct.pdf p.19 | 12957_Credit-Facilities.pdf p.15 | 12942_Responsible-Business-Conduct.pdf p.14 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.7</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>CHECK</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>found 5000; missing 30days</t>
+          <t>all key figures present (30days, 5000)</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>12.2</v>
+        <v>7.5</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>The cap on default loss guarantee (DLG) cover is five per cent of the total amount disbursed out of the loan portfolio at any given time [1]. For example, if a portfolio of ₹40 crore is earmarked, the DLG cover ceiling is ₹2 crore (5% of ₹40 crore) [3]. This cap applies to both explicit and implicit guarantee arrangements [1].</t>
+          <t>The cap on default loss guarantee (DLG) cover in digital lending is five per cent of the total amount disbursed from the loan portfolio. This applies to NBFCs, including those engaged in digital lending, as specified in the regulations. For example, a DLG set of ₹40 crore would have a DLG cover ceiling of ₹2 crore (5% of ₹40 crore), which activates proportionally as loans are disbursed [1]. The cap is calculated based on disbursed amounts, not the total portfolio, and remains fixed for the DLG set [1]. No separate cap for digital lending is mentioned in the passages.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>12957_Credit-Facilities.pdf p.24 | 12957_Credit-Facilities.pdf p.25 | 12957_Credit-Facilities.pdf p.25 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.14 | 12957_Credit-Facilities.pdf p.26 | 12952_Transfer-and-Distribution-of-Credit-Risk.pdf p.36</t>
+          <t>12957_Credit-Facilities.pdf p.24 | 12957_Credit-Facilities.pdf p.25 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.14 | 12957_Credit-Facilities.pdf p.26 | 12957_Credit-Facilities.pdf p.8 | 12952_Transfer-and-Distribution-of-Credit-Risk.pdf p.36</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>The minimum cooling-off period for digital loans is one day, as stipulated in [1]. The borrower must be given an explicit option to exit the loan during this period without penalty, and the NBFC determines the exact duration, which cannot be less than one day.</t>
+          <t>The minimum cooling-off period for digital loans is one day, as determined by the NBFC's credit policy, subject to the period not being less than one day [1].</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -1413,14 +1413,14 @@
       <c r="F19" t="inlineStr">
         <is>
           <t>The credit concentration limits for a Middle Layer NBFC are:  
-- **25 per cent of its Tier 1 capital** to a single party;  
-- **40 per cent of its Tier 1 capital** to a single group of parties.  
-These norms apply to NBFCs in the Middle Layer (NBFC-ML) and are specified in paragraph 13 of the concentration risk management directions [3].</t>
+- **25 per cent of its Tier 1 capital** to a single party; and  
+- **40 per cent of its Tier 1 capital** to a single group of parties [1].  
+These norms apply to NBFCs except NBFC-IFC and NBFC-UL (Upper Layer), as specified in the context [1].</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>12953_Concentration-Risk-Management.pdf p.2 | 12954_Credit-Risk-Management.pdf p.13 | 12953_Concentration-Risk-Management.pdf p.10 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.7 | 12953_Concentration-Risk-Management.pdf p.10 | 12953_Concentration-Risk-Management.pdf p.8</t>
+          <t>12953_Concentration-Risk-Management.pdf p.10 | 12954_Credit-Risk-Management.pdf p.13 | 12953_Concentration-Risk-Management.pdf p.8 | 12953_Concentration-Risk-Management.pdf p.2 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.7 | 12953_Concentration-Risk-Management.pdf p.10</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>9.9</v>
+        <v>11</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NBFCs must report credit information to credit information companies **monthly** for wilful defaulters (Annex II) and large defaulters (Annex I) [1], [2]. Additional reporting occurs **quarterly** for total exposure in specific credit risk transfer scenarios [4].</t>
+          <t>NBFCs must report credit information to credit information companies **monthly** for wilful defaulters [1] and large defaulters [2]. For structured digital lending products, reporting is required "irrespective of its nature / tenor" under the same monthly framework [5]. Quarterly reporting applies only to specific credit risk transfer exposures [4].</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>An NBFC identified in the Upper Layer (NBFC-UL) must be mandatorily listed within **three years** of identification [1], [2]. This requirement applies unless the NBFC-UL is fully owned and controlled by the Government [1].</t>
+          <t>An NBFC identified in the Upper Layer must list its equity shares within three years of identification [1], [2].</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>12945_Financial-Statements-Presentation-Disclosures.pdf p.47 | 12960_Governance.pdf p.17 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.14 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.15 | 12949_Asset-Liability-Management.pdf p.10 | 12953_Concentration-Risk-Management.pdf p.2</t>
+          <t>12945_Financial-Statements-Presentation-Disclosures.pdf p.47 | 12960_Governance.pdf p.17 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.14 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.15 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.15 | 12953_Concentration-Risk-Management.pdf p.2</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>No, collection staff may not call borrowers late at night unless explicitly authorized by the borrower. Calls are generally restricted to 09:30–19:00 hours [4][6], and exceptions require the borrower's written or oral consent [6][4]. Persistent calls outside these hours, including late at night, are prohibited unless authorized [2][5].</t>
+          <t>No, collection staff cannot call borrowers late at night. The guidelines specify that recovery agents must contact borrowers between 8:00 a.m. and 7:00 p.m. [3](6)(e), and persistently calling before 9:00 a.m. or after 6:00 p.m. is explicitly prohibited as a harsh recovery practice [2](91)(2). Additionally, borrowers may request to avoid calls at specific times, which must be honored [3](6)(f).</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>12942_Responsible-Business-Conduct.pdf p.28 | 12942_Responsible-Business-Conduct.pdf p.27 | 12939_Housing-Finance-Companies.pdf p.70 | 12939_Housing-Finance-Companies.pdf p.59 | 12942_Responsible-Business-Conduct.pdf p.9 | 12939_Housing-Finance-Companies.pdf p.58</t>
+          <t>12942_Responsible-Business-Conduct.pdf p.28 | 12942_Responsible-Business-Conduct.pdf p.27 | 12939_Housing-Finance-Companies.pdf p.70 | 12942_Responsible-Business-Conduct.pdf p.9 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.28 | 12939_Housing-Finance-Companies.pdf p.72</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -1627,7 +1627,8 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>If a borrower pays off the overdue interest but still owes some principal, the account cannot be taken out of NPA status until **entire arrears of interest and principal** are paid. According to paragraph 24 of [1], loan accounts classified as NPAs may be upgraded as "standard" assets **only if entire arrears of interest and principal are paid**. Similarly, paragraph 25 of [1] specifies that upgrades from NPA to standard require repayment of **all arrears** across all credit facilities. Thus, partial payments (e.g., only interest) do not suffice to remove the NPA classification.</t>
+          <t>If a borrower pays off the overdue interest but still owes some principal, the account cannot be upgraded from NPA to standard asset unless **entire arrears of interest and principal** are paid. Paragraph 24 explicitly states that NPAs may be upgraded to standard assets only upon full repayment of all arrears (interest and principal) [2]. Partial payments (e.g., paying overdue interest but leaving principal unpaid) do not satisfy this condition. 
+Additionally, paragraph 43 defines NPA based on overdue interest or principal exceeding 90/180 days, but upgradation requires resolution of **all** outstanding obligations [4]. Thus, residual principal would keep the account in NPA status.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1646,7 +1647,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>17.3</v>
+        <v>10.2</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1680,7 +1681,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>When rates go up, NBFCs **may** provide floating-rate borrowers the option to switch to a fixed rate, but this is not mandatory. The policy allows NBFCs to offer this switch as part of their Board-approved framework [1][2]. Borrowers are given the choice to switch, but the decision rests with the NBFC, not a requirement. Thus, switching is optional, not obligatory.</t>
+          <t>When rates go up, floating-rate borrowers are **not required** to switch to a fixed rate. The NBFC may, at its option, provide the choice to switch to a fixed rate as per its Board-approved policy [1]. However, this switch is optional, and borrowers are not mandatorily obligated to do so. The policy may specify the number of times a borrower can switch during the loan tenor [1]. Similarly, the policy on reset of floating rate personal loans explicitly includes the option to switch between fixed and floating rates but does not enforce it [2].</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1699,7 +1700,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -1733,12 +1734,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>No, penal interest cannot be added when a customer pays late. Penal charges for non-compliance, including late payments, must be levied as separate charges and not as penal interest added to the interest rate. Interest may still be charged on the outstanding amount (adjusted for payments/refunds) at the contracted rate, but this is distinct from penal interest, which is explicitly prohibited [1][2]. Late payment charges are treated as penal charges, not penal interest, and are applied only to the outstanding amount after the due date [3][6].</t>
+          <t>No, penal interest cannot be added when a customer pays late. Penal charges for non-compliance (e.g., late repayment) are distinct from penal interest and must be levied as 'penal charges' without capitalization (i.e., no further interest on such charges) [1][2]. However, normal interest on unpaid principal or unpaid EMI may still be charged at the contracted rate until remediation [1]. For credit cards, late payment charges are applied on the outstanding amount after the due date, but interest is only levied on the adjusted outstanding amount, not the total amount due [3].</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>12942_Responsible-Business-Conduct.pdf p.14 | 12942_Responsible-Business-Conduct.pdf p.14 | 12956_Credit-Cards-Issuance-and-Conduct.pdf p.13 | 12942_Responsible-Business-Conduct.pdf p.35 | 12942_Responsible-Business-Conduct.pdf p.8 | 12956_Credit-Cards-Issuance-and-Conduct.pdf p.15</t>
+          <t>12942_Responsible-Business-Conduct.pdf p.14 | 12942_Responsible-Business-Conduct.pdf p.14 | 12956_Credit-Cards-Issuance-and-Conduct.pdf p.13 | 12942_Responsible-Business-Conduct.pdf p.8 | 12942_Responsible-Business-Conduct.pdf p.35 | 12956_Credit-Cards-Issuance-and-Conduct.pdf p.15</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1752,7 +1753,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -1786,12 +1787,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>No, entities do not decide their layer classification. The Reserve Bank of India (RBI) specifically identifies NBFCs for the Upper Layer annually based on supervisory criteria [5], and movements between layers depend on regulatory assessments, not self-determination [1][2][6].</t>
+          <t>No, the classification of an NBFC into the Upper Layer is determined by the Reserve Bank of India (RBI) based on scale-based regulatory parameters, not self-declared. Once identified as NBFC-UL (Upper Layer), the entity must comply with mandated timelines and regulatory requirements, including submitting a Board-approved roadmap for compliance with listed company standards [1][6]. The transition and categorization are governed by RBI's directives, not autonomous decisions by the NBFC.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>12937_Core-Investment-Companies.pdf p.6 | 12939_Housing-Finance-Companies.pdf p.6 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.11 | 12939_Housing-Finance-Companies.pdf p.26 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.11 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13</t>
+          <t>12945_Financial-Statements-Presentation-Disclosures.pdf p.47 | 12937_Core-Investment-Companies.pdf p.6 | 12939_Housing-Finance-Companies.pdf p.6 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.15 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.11 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.14</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1805,7 +1806,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -1839,12 +1840,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>No, a foreclosure fee cannot be charged for prepaying a floating-rate personal loan early. According to [4] E.34(1), NBFCs shall not levy pre-payment charges on floating rate loans granted for purposes other than business to individuals. Since the loan is for a salaried customer (personal use), this provision explicitly prohibits pre-payment charges. Additionally, [1] 163(1) clarifies that pre-payment levies are barred for floating-rate housing loans pre-closed from any source, which aligns with this scenario.</t>
+          <t>No, a foreclosure fee cannot be charged for prepaying a floating-rate personal loan to a salaried individual. According to paragraph 34(1) of the Reserve Bank of India (Non-Banking Financial Companies - Responsible Business Conduct) Directions, 2025, NBFCs shall not levy pre-payment charges on floating rate loans granted for purposes other than business to individuals [3]. Since the loan is for a personal purpose (salaried individual), this provision explicitly prohibits pre-payment charges, including foreclosure fees.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>12939_Housing-Finance-Companies.pdf p.66 | 12942_Responsible-Business-Conduct.pdf p.16 | 12942_Responsible-Business-Conduct.pdf p.35 | 12942_Responsible-Business-Conduct.pdf p.18 | 12942_Responsible-Business-Conduct.pdf p.36 | 12942_Responsible-Business-Conduct.pdf p.35</t>
+          <t>12939_Housing-Finance-Companies.pdf p.66 | 12942_Responsible-Business-Conduct.pdf p.16 | 12942_Responsible-Business-Conduct.pdf p.18 | 12942_Responsible-Business-Conduct.pdf p.35 | 12942_Responsible-Business-Conduct.pdf p.36 | 12939_Housing-Finance-Companies.pdf p.53</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1858,7 +1859,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -1892,7 +1893,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>The context passages do not explicitly address whether a lending app partner can collect EMIs into its own bank account and forward them to the lender. However, [4] specifies that loan repayments must be made into the NBFC's bank account, implying that direct collection into the NBFC's account is permissible. If the app partner is acting as the NBFC, this would align with the requirement. For third-party entities (e.g., LSPs), the passages do not clarify this scenario. Thus, the answer depends on the app partner's role, which is not explicitly defined in the provided texts.</t>
+          <t>The NBFC must ensure that loan disbursements are made directly into the borrower's bank account, except for specific statutory or regulatory cases [4]. Funds collected from borrowers (e.g., EMIs) must be transferred through escrow accounts operated by a bank trustee, with strict rules against using these accounts for unauthorized purposes [3]. The lending app partner, if acting as a Loan Servicing Provider (LSP), would handle collections via the escrow mechanism, not their own bank account. Thus, collecting EMIs into the app partner's own account would violate the prescribed funds transfer mechanism and disbursement rules.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1911,7 +1912,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>12.1</v>
+        <v>7.7</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -1945,7 +1946,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>The customer has 30 days from the date of filing the complaint with the NBFC to receive a response. If the NBFC does not respond within this period or if the complainant is unsatisfied with the resolution, they can approach the RBI Ombudsman [1], [3], [6].</t>
+          <t>The customer has 30 days to resolve a complaint before approaching the RBI Ombudsman. If the card-issuer does not respond within 30 days after filing the complaint or rejects it wholly/partly, the customer can escalate to the Ombudsman [1]. This timeline is also stipulated for NBFCs in cases where complaints are rejected or unresolved [3], and reiterated for digital lending grievances [6].</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1964,7 +1965,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>7.7</v>
+        <v>5.9</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -1998,12 +1999,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>No. The NBFC shall not outsource the Internal Audit function entirely [1]. While experts can be hired on a contractual basis for specific tasks, ownership of audit reports must remain with the internal audit function [1]. Additionally, core management functions like Internal Audit are explicitly prohibited from being outsourced [3].</t>
+          <t>No, the NBFC shall not outsource the entire internal audit function. The Internal Audit function is explicitly prohibited from being outsourced, and ownership of audit reports must remain with regular functionaries of the Internal Audit function [1]. Core management functions, including internal audit, are also listed as activities that shall not be outsourced [3]. While external experts may be hired for specific tasks (e.g., IT/IS audit) under certain conditions, the entire function cannot be transferred to an outside firm.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>13589_SUP-Internal-Audit-Function.pdf p.11 | 12941_Managing-Risks-in-Outsourcing.pdf p.13 | 12941_Managing-Risks-in-Outsourcing.pdf p.12 | 13592_SUP-Cybersecurity-Technology-Risk-Resilience.pdf p.23 | 12939_Housing-Finance-Companies.pdf p.62 | 12941_Managing-Risks-in-Outsourcing.pdf p.23</t>
+          <t>13589_SUP-Internal-Audit-Function.pdf p.11 | 12941_Managing-Risks-in-Outsourcing.pdf p.13 | 12941_Managing-Risks-in-Outsourcing.pdf p.12 | 13592_SUP-Cybersecurity-Technology-Risk-Resilience.pdf p.23 | 12941_Managing-Risks-in-Outsourcing.pdf p.23 | 13588_SUP-Statutory-Audit.pdf p.11</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2017,7 +2018,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>8.300000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -2051,26 +2052,26 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>The Compliance function must be headed by a Chief Compliance Officer (CCO) as per [1], but the passages do not specify whether a separate compliance head is required beyond the CCO. Regarding rotation, the text does not mention annual rotation of compliance heads. Rotation rules apply to statutory auditors (e.g., audit firms cannot be reappointed in the same NBFC for six years after a term [3]), but no such requirement is stated for compliance heads.</t>
+          <t>The Compliance function must be headed by a Chief Compliance Officer (CCO) as per [1], which mandates the CCO to head the Compliance Department. However, the passages do not specify any requirement for annual rotation of the CCO or compliance heads. Rotation policies mentioned in the context apply to statutory auditors (e.g., audit firms cannot be reappointed in the same NBFC for six years after a term [3]), but no such rule is stated for compliance heads. Thus, while a separate compliance head is required, the context does not support the claim that they must be rotated annually.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>13593_SUP-Compliance-Function.pdf p.7 | 12939_Housing-Finance-Companies.pdf p.48 | 13588_SUP-Statutory-Audit.pdf p.13 | 12960_Governance.pdf p.29 | 13593_SUP-Compliance-Function.pdf p.5 | 12932_Non-Operative-Financial-Holding-Companies.pdf p.8</t>
+          <t>13593_SUP-Compliance-Function.pdf p.7 | 12939_Housing-Finance-Companies.pdf p.48 | 13588_SUP-Statutory-Audit.pdf p.13 | 12960_Governance.pdf p.29 | 13593_SUP-Compliance-Function.pdf p.5 | 13593_SUP-Compliance-Function.pdf p.7</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CHECK</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>no numeric facts to compare - read the answer yourself</t>
+          <t>declined to answer an in-scope question - retrieval likely missed</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2104,7 +2105,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yes, loan terms must be explained in a language the borrower understands. The Key Facts Statement (KFS) must be provided in a language understood by the borrower [1], and the contents of the KFS must be explained to the borrower with an acknowledgment of understanding [1]. Additionally, loan terms and conditions must be conveyed in the vernacular language or a language as understood by the borrower [2], and all communications, including terms and conditions, must be in the language of the region or chosen by the borrower [6]. For illiterate borrowers, important terms must be explained in the presence of a witness [6].</t>
+          <t>Yes, loan terms must be explained in a language understood by the borrower. The Key Facts Statement (KFS) must be provided in a language understood by borrowers [1]. Loan agreements and terms must be conveyed in the vernacular language as understood by the borrower [2]. The Fair Practices Code (FPC) and loan agreements for microfinance loans must also be in a language understood by the borrower [3]. Notices regarding changes in terms and conditions must be in the vernacular language or a language as understood by the borrower [4]. All communications to the borrower, including terms and conditions, must be in the vernacular language or a language chosen by the borrower [5].</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2123,7 +2124,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -2157,12 +2158,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yes, before selling a repossessed vehicle, the borrower must be given a notice period as specified in the contract/loan agreement. The terms and conditions must include a provision for a notice period before taking possession [1], and the borrower is also given a final chance to repay the loan before the sale/auction of the property [1]. Additionally, the procedure for sale/auction of the property must be followed, which inherently involves notifying the borrower [2].</t>
+          <t>Yes, before selling a repossessed vehicle, the borrower must be given a final chance to repay the loan. The terms and conditions of the loan agreement must include a provision ensuring this final opportunity for repayment before the sale/auction of the property [1]. Additionally, the notice period before taking possession of the security must be observed, which inherently involves warning the borrower [3]. These requirements are part of the legally enforceable clauses mandated for NBFCs and HFCs [1][4].</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>12942_Responsible-Business-Conduct.pdf p.10 | 12939_Housing-Finance-Companies.pdf p.72 | 12939_Housing-Finance-Companies.pdf p.66 | 12939_Housing-Finance-Companies.pdf p.70 | 12942_Responsible-Business-Conduct.pdf p.28 | 12946_Wilful-Defaulters-and-Large-Defaulters.pdf p.11</t>
+          <t>12942_Responsible-Business-Conduct.pdf p.10 | 12939_Housing-Finance-Companies.pdf p.66 | 12939_Housing-Finance-Companies.pdf p.72 | 12939_Housing-Finance-Companies.pdf p.70 | 12942_Responsible-Business-Conduct.pdf p.36 | 12942_Responsible-Business-Conduct.pdf p.28</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2176,7 +2177,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -2210,7 +2211,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>A depositor cannot request repayment of a public deposit within two months of investment, as premature repayment is generally restricted to cases where the NBFC permits it **after three months** from the deposit date [1]. Exceptions exist for specific emergent circumstances (e.g., critical illness) or "tiny deposits," but these are not applicable unless explicitly stated [3]. Without such exceptions, repayment before three months is not allowed.</t>
+          <t>A depositor cannot request repayment of a public deposit within two months of investment, as premature repayment by an NBFC is generally restricted to cases where the depositor requests it **after three months** from the date of deposit [1]. Exceptions exist only for specific emergent circumstances, such as critical illness (allowing 100% repayment before three months) or "tiny deposits" (allowing full repayment for individual depositors in certain cases) [3]. Without such exceptions, repayment before three months is not permitted.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2229,7 +2230,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -2263,7 +2264,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Yes, different interest rates can be charged to borrowers who seem similar, provided the differentiation is based on relevant factors and transparently disclosed. For instance, NBFCs are required to determine interest rates considering factors like cost of funds, margin, and risk premium, and disclose the rationale for different rates to different categories of borrowers [1]. Similarly, credit card issuers may charge differential interest rates based on payment/default history, with transparency in the methodology and rationale [5]. However, penal charges within the same product category may vary based on loan amount, but must remain reasonable and non-discriminatory [3]. Such differentiation must adhere to regulatory norms and ensure no capitalization of charges or negative amortization [1][5].</t>
+          <t>Yes, different interest rates can be charged to borrowers who seem similar, provided the differentiation is based on relevant factors such as risk profile, cost of funds, and other criteria outlined in the regulations. For instance, [1] mandates that NBFCs determine interest rates considering factors like cost of funds, margin, and risk premium, and disclose the rationale for different rates to different borrower categories. Similarly, [2] states that the blended interest rate is calculated based on the risk profile of the borrower and the proportionate funding share of respective REs under CLA. However, such differentiation must be transparent, with clear disclosure of the methodology and rationale, as required in [1] and [5]. Additionally, [3] specifies that penal charges (not interest rates) within the same product category must be uniform and non-discriminatory, but this does not preclude rate variations based on justified factors. Thus, while similar borrowers may have different rates if their risk profiles or other relevant factors differ, the practice must adhere to disclosure and transparency requirements.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2282,7 +2283,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -2316,12 +2317,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yes, there is a cap. The NBFC must ensure that loan repayment outflows do not exceed 50 per cent of the monthly household income [1]. This cap applies to all existing and new loans, and future income from assets financed by microfinance loans is excluded from the calculation [1].</t>
+          <t>Yes, there is a cap. The NBFC must ensure that the outflows for repayment of monthly loan obligations of a household do not exceed **50 per cent of the monthly household income** [1]. This limit applies to all outstanding loans, including both principal and interest, and excludes future income from assets financed by the loan [1].</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>12957_Credit-Facilities.pdf p.36 | 12957_Credit-Facilities.pdf p.2 | 12957_Credit-Facilities.pdf p.34 | 12947_Resolution-of-Stressed-Assets.pdf p.54 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.22 | 12957_Credit-Facilities.pdf p.15</t>
+          <t>12957_Credit-Facilities.pdf p.36 | 12957_Credit-Facilities.pdf p.2 | 12957_Credit-Facilities.pdf p.34 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.10 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.22 | 12934_Peer-to-Peer-Lending-Platform.pdf p.10</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2369,17 +2370,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>The provisions of Chapter III (outsourcing arrangements) apply to your Middle Layer NBFC's app-based personal loans through a lending service provider, as these provisions cover material outsourcing for financial services like loan origination [1]. Additionally, Chapter IV and IT-specific provisions in Chapter II apply to Middle Layer NBFCs [1]. For outsourcing to a service provider, the scope of Chapter III includes activities such as applications processing, document processing, and back-office activities [1]. If the app-based lending involves IT outsourcing (e.g., app development, data processing), the IT-specific provisions in Chapter II (e.g., Board-level IT outsourcing policy) also apply [1]. 
-Specifically, the following passages govern your case:  
-- **Chapter III** (outsourcing scope) [1].  
-- **Chapter IV** and IT-specific provisions in **Chapter II** (for Middle Layer NBFCs) [1].  
-- **Paragraphs 6–19, 23–33, and 50–52** from the relevant Directions, which apply to Middle Layer NBFCs [5].  
-Exemptions or additional rules depend on whether the service provider is affiliated or unrelated, and whether IT infrastructure is involved [1].</t>
+          <t>The applicable provisions for a Middle Layer NBFC launching app-based personal loans through a service provider are:  
+- **Chapter III** of the Directions, which covers material outsourcing arrangements, including app-based services (e.g., loan processing, data handling) [1].  
+- **Chapter IV** and IT-specific provisions in **Chapter II** (e.g., Board-level IT outsourcing policy) [1].  
+- **Paragraphs 53–57** of the Directions, applicable to Middle Layer and above [4].  
+- **Provisions for NBFCs in Middle Layer** under the 2025 Regulatory Structure [1][2][4][6].  
+These apply because Middle Layer NBFCs are explicitly covered under these chapters and paragraphs, and the outsourcing of app-based personal loans falls under "material outsourcing arrangements" [1].</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>12941_Managing-Risks-in-Outsourcing.pdf p.4 | 12953_Concentration-Risk-Management.pdf p.2 | 12931_Miscellaneous.pdf p.2 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.2 | 12961_Undertaking-of-Financial-Services.pdf p.2 | 12946_Wilful-Defaulters-and-Large-Defaulters.pdf p.3</t>
+          <t>12941_Managing-Risks-in-Outsourcing.pdf p.4 | 12953_Concentration-Risk-Management.pdf p.2 | 12931_Miscellaneous.pdf p.2 | 12961_Undertaking-of-Financial-Services.pdf p.2 | 12946_Wilful-Defaulters-and-Large-Defaulters.pdf p.3 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.2</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2393,7 +2394,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>10.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -2427,12 +2428,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>When your Base Layer NBFC's assets cross ₹1,000 crore, you will be classified as an NBFC in the Middle Layer, triggering regulatory requirements under paragraph 34 of the Directions [2]. This includes compliance with prudential norms, reporting obligations, and applicable directions for Middle Layer NBFCs. If your asset size temporarily falls below ₹1,000 crore later, you must still comply with Middle Layer regulations until the next audited balance sheet is submitted [2]. Additionally, if you are a Type I NBFC (e.g., NBFC-P2P, NBFC-AA, etc.), there is no ceiling on dividend payout ratios, but other NBFC types (e.g., CIC, SPD) face caps [3]. Group consolidation rules apply only if you are part of a common Group [1].</t>
+          <t>When your NBFC crosses ₹1,000 crore in asset size, it will transition from Base Layer (NBFC-BL) to Middle Layer (NBFC-ML) classification. This triggers compliance with regulatory requirements under paragraph 34 of the Directions, including stricter reporting and operational standards applicable to NBFC-ML [1]. Additionally, all non-deposit taking NBFCs attaining this threshold must adhere to extant NBFC-ML regulations, regardless of when the size is achieved [1]. If part of a group, consolidated assets exceeding ₹1,000 crore would also classify individual NBFCs in the group as NBFC-ML [2]. Note that temporary dips below ₹1,000 crore due to fluctuations do not exempt compliance with ML requirements until the next audited balance sheet is submitted [1].</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.12 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13 | 12944_Declaration-of-Dividends.pdf p.6 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.11 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.12</t>
+          <t>12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.12 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.11 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13 | 12961_Undertaking-of-Financial-Services.pdf p.2 | 12947_Resolution-of-Stressed-Assets.pdf p.35</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2446,7 +2447,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>13.6</v>
+        <v>10.1</v>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
@@ -2480,12 +2481,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Yes, a non-deposit-taking Middle Layer NBFC can start accepting public deposits, but must comply with specific regulations. To do so, it must:  
-1. Meet the minimum net owned funds (NOF) requirements and prudential norms [4].  
-2. Comply with the Reserve Bank of India (Non-Banking Financial Companies - Acceptance of Public Deposits) Directions, 2025, including limits on deposit acceptance (up to 1.5 times NOF) and restrictions on renewing matured deposits without depositor consent [6].  
-3. Transition from "non-deposit-taking" to "deposit-taking" status, which would subject it to Chapter IV of the Directions (applicable to deposit-taking NBFCs) and other prudential regulations [2].  
-4. Pass a board resolution confirming non-acceptance of public deposits prior to commencement of the financial year, and ensure compliance with audit requirements [4][5].  
-Failure to meet these criteria would restrict renewal or acceptance of fresh deposits beyond the 1.5×NOF limit [6].</t>
+          <t>To start accepting public deposits, a non-deposit-taking Middle Layer NBFC must comply with the prudential norms and regulatory framework outlined in the Reserve Bank of India (Non-Banking Financial Companies - Acceptance of Public Deposits) Directions, 2025. Specifically:  
+1. **Eligibility**: The NBFC must meet the minimum net owned funds (NOF) requirements and comply with all prudential norms, including capital adequacy ratios and asset classification standards [4][6].  
+2. **Deposit Limits**: It may accept or renew public deposits up to **1.5 times its NOF**. Exceeding this limit would restrict renewal or acceptance of fresh deposits until compliance is achieved [6].  
+3. **Classification**: Transitioning from non-deposit-taking to deposit-taking status likely requires reclassification under the RBI’s scale-based regulation framework (e.g., from Type I NBFC to Type II NBFC or another category) [1][2].  
+4. **Reporting**: The NBFC must submit quarterly statements of capital funds, risk assets, and risk asset ratios (DNBS03) to the RBI [5].  
+**Conclusion**: Yes, a non-deposit-taking Middle Layer NBFC can start accepting public deposits **if it meets the NOF thresholds, prudential norms, and regulatory requirements**, and obtains necessary approvals from the RBI.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2504,7 +2505,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
@@ -2538,12 +2539,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>The LTV ratio for gold loans is determined by the NBFC's credit policy as per the regulations, but the exact permissible maximum LTV ratio is not specified in the provided contexts [1][4]. The policy must include appropriate LTV ratios, but the specific figure is left to the NBFC's discretion under the framework outlined in Chapter IV of the Directions [3].</t>
+          <t>The applicable LTV ratio for gold loans is determined by the NBFC's credit policy under the Reserve Bank of India (Non-Banking Financial Companies - Credit Facilities) Directions, 2025, as amended [5]. The exact percentage is not specified in the provided contexts, but the policy must include "appropriate single borrower limits and aggregate limits for the portfolio of loans against collateral of jewellery, ornaments or coins made of gold or silver" and define the maximum permissible LTV ratio [1]. For specific thresholds, reference to the Directions is required.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>12957_Credit-Facilities.pdf p.29 | 12957_Credit-Facilities.pdf p.47 | 12957_Credit-Facilities.pdf p.1 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.11 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.10 | 12953_Concentration-Risk-Management.pdf p.2</t>
+          <t>12957_Credit-Facilities.pdf p.29 | 12957_Credit-Facilities.pdf p.47 | 12957_Credit-Facilities.pdf p.1 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.10 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.11 | 12953_Concentration-Risk-Management.pdf p.2</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2557,7 +2558,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>11</v>
+        <v>17.8</v>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
@@ -2592,15 +2593,16 @@
       <c r="F41" t="inlineStr">
         <is>
           <t>To ensure compliance when outsourcing collections to an agency, an NBFC must:  
-- Define terms and conditions in a legally binding agreement, including service standards, access to books/records, and monitoring mechanisms [1][3].  
-- Ensure the service provider maintains confidentiality, incorporates liability for data breaches, and includes contingency plans for business continuity [1][3].  
-- Grant the NBFC rights to audit the service provider, access audit trails, and allow RBI inspections of the service provider’s operations [1][2][3].  
-- Include provisions for subcontractor approvals, data storage in India (if applicable), and reporting of material adverse events (e.g., data breaches) [1][3][5].  
-- Ensure the service provider complies with the Information Technology Act, 2000, and other legal requirements to protect customer data [3].  
-- Maintain post-termination confidentiality of customer information and ensure the service provider preserves documents per regulatory obligations [1][3].  
-- Avoid outsourcing arrangements that could impede RBI’s supervisory functions or weaken internal controls [4].  
-- If the agency is offshore, ensure records remain accessible to the NBFC and RBI, and the offshore jurisdiction does not restrict RBI’s access to Indian operations [5].  
-- Ensure the service provider is not owned or controlled by NBFC directors or their relatives (unless approved by the Board with oversight) [6].</t>
+- Define terms and conditions in a legally binding written agreement, vetted by legal counsel, and include service standards, access to records, and monitoring mechanisms [1][3].  
+- Ensure the service provider maintains confidentiality controls, data security, and liability for breaches [1][3][4].  
+- Grant the NBFC rights to audit the service provider, access audit trails, and inspect its operations, including post-termination [1][2][3].  
+- Include provisions for subcontractor approval, business continuity plans, and contingency measures [1][3][61].  
+- Maintain data storage in India (if applicable) and ensure compliance with the Information Technology Act, 2000, and other legal requirements [3][4].  
+- Prohibit the service provider from being owned or controlled by NBFC directors or their relatives, unless approved by the Board [6].  
+- Report cyber incidents to the NBFC within six hours of detection, and ensure the NBFC reports them to the RBI within six hours [61].  
+- Ensure outsourcing does not impede RBI’s supervisory functions or compromise internal controls, reputation, or regulatory obligations [4].  
+- For offshore providers, verify jurisdictional compliance, data storage in India, and prevent unauthorized access to Indian operations by foreign regulators [5].  
+- Include post-termination obligations, such as preserving documents and maintaining customer confidentiality [1][3].</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2619,7 +2621,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>9.9</v>
+        <v>12.9</v>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
@@ -2653,18 +2655,18 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>The Middle Layer NBFC with 12 branches must comply with the following core technology system requirements:  
-- A **Board-approved IT/IS policy** covering basic security aspects (physical/logical access controls, password policies, user roles, maker-checker concepts, and robust cybersecurity controls) [2].  
-- **Periodic risk assessments** for digital payment systems, including technology stack evaluation, third-party oversight, and integration risks [1].  
-- A **Business Continuity Plan (BCP)** policy approved by the Board, with annual reviews and periodic testing of data backups [2].  
-- **Robust IT infrastructure** with capacity management plans to handle transaction volumes and customer growth, including periodic reviews of IT/security architecture [1].  
-- **Secure customer communication** mechanisms, including clear terms and conditions, fraud reporting tools, and anti-malware guidance [4].  
-These requirements ensure compliance with cybersecurity, operational resilience, and customer protection standards for Middle Layer NBFCs.</t>
+          <t>The Middle Layer NBFC must comply with core technology system requirements outlined in the context passages. Specifically:  
+- A **Board-approved IT/IS policy** is mandated, covering basic security aspects like physical/logical access controls, password policies, user roles, and maker-checker concepts [2].  
+- The IT strategy must ensure a **robust capacity management plan** to handle transaction volumes and customer growth, with periodic reviews of IT/IT security architecture and technology platforms [1].  
+- **Backup and testing** of data and applications are required at least **half-yearly** to ensure recovery without loss of transactions or audit trails [1].  
+- The **Early Warning Signals (EWS) framework** must be integrated with **Core Banking Solution (CBS)** or other operational systems for fraud risk management [6].  
+- **Periodic risk assessments** must evaluate technology stacks, third-party dependencies, and cybersecurity controls, with updates to the Risk and Control Self-Assessment (RCSA) as needed [1].  
+These requirements apply regardless of the number of branches, including 12 branches.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>13591_SUP-Digital-Payment-Security-Controls.pdf p.8 | 13592_SUP-Cybersecurity-Technology-Risk-Resilience.pdf p.10 | 12957_Credit-Facilities.pdf p.15 | 13591_SUP-Digital-Payment-Security-Controls.pdf p.18 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.12 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.21</t>
+          <t>13591_SUP-Digital-Payment-Security-Controls.pdf p.8 | 13592_SUP-Cybersecurity-Technology-Risk-Resilience.pdf p.10 | 12957_Credit-Facilities.pdf p.15 | 13591_SUP-Digital-Payment-Security-Controls.pdf p.18 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.12 | 13590_SUP-Fraud-Risk-Management.pdf p.10</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2678,7 +2680,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -2712,8 +2714,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Under the Reserve Bank of India (Non-Banking Financial Companies - Responsible Business Conduct) Directions, 2025, a Middle Layer NBFC lending floating-rate term loans to micro and small enterprises (MSEs) **cannot charge prepayment fees** if the sanctioned amount is **up to ₹50 lakh**. Specifically, paragraph 34(2)(ii) states: *"an NBFC-Middle Layer shall not levy any pre-payment charges on loans with sanctioned amount/ limit up to ₹50 lakh"* [1]. 
-For loans exceeding ₹50 lakh, the regulations do not explicitly prohibit prepayment charges, but the general rule in paragraph 34(1) applies to floating-rate loans for purposes other than business-to-individuals, which includes MSEs. However, since MSEs fall under business purposes, the stricter restriction in 34(2)(ii) governs loans up to ₹50 lakh. If the loan amount exceeds ₹50 lakh, the NBFC may charge prepayment fees, provided they comply with other applicable rules (e.g., disclosure requirements in paragraph 34(8)).</t>
+          <t>No, a Middle Layer NBFC cannot levy pre-payment charges on floating rate term loans sanctioned for business purposes to micro and small enterprises (MSEs) with a sanctioned amount/limit up to ₹50 lakh [1](#1). This prohibition applies irrespective of the source of funds used for pre-payment and without a minimum lock-in period [1](#1).</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2723,16 +2724,16 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>CHECK</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>found 2025; missing 2026.</t>
+          <t>none of the expected figures appear (2025, 2026.)</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>16.5</v>
+        <v>7.8</v>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -2767,16 +2768,18 @@
       <c r="F44" t="inlineStr">
         <is>
           <t>The main new obligations for an NBFC identified as Upper Layer (NBFC-UL) include:  
-1. **Mandatory listing within three years** of identification, with a Board-approved roadmap for compliance with listed company disclosure requirements under SEBI Regulations [1][3].  
-2. **Board-approved policy and implementation plan** to adopt the enhanced regulatory framework, with compliance to be achieved within 24 months from the date of RBI classification advice [2].  
-3. **Enhanced regulatory requirements** applicable for at least five years post-classification, unless the NBFC voluntarily adjusts operations under a Board-approved policy [5].  
-4. **Disclosure obligations** aligned with listed companies, even before actual listing, as per the Board-approved policy [3].  
-Government-owned NBFC-ULs are exempt from some provisions [1][3].</t>
+1. **Mandatory listing within three years** of identification [1][3].  
+2. **Board-approved roadmap** for compliance with listed company disclosure requirements under SEBI’s 2015 regulations, even before actual listing [1][3].  
+3. **Implementation plan** to adhere to enhanced regulatory framework within 24 months from the date of RBI classification advice [2].  
+4. **Submission of the roadmap** to the Reserve Bank for supervisory review [2].  
+5. **Subject to enhanced regulatory requirements** for at least five years post-classification, unless exiting via voluntary strategic adjustments [4].  
+6. Compliance with **concentration risk management norms** applicable to NBFC-ULs, including limits on large exposures (10% of eligible capital base) [5][6].  
+Government-owned NBFC-ULs are exempt from some provisions [1][5].</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>12945_Financial-Statements-Presentation-Disclosures.pdf p.47 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.14 | 12960_Governance.pdf p.17 | 12953_Concentration-Risk-Management.pdf p.2 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.15 | 12943_Know-Your-Customer.pdf p.65</t>
+          <t>12945_Financial-Statements-Presentation-Disclosures.pdf p.47 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.14 | 12960_Governance.pdf p.17 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.15 | 12953_Concentration-Risk-Management.pdf p.2 | 12953_Concentration-Risk-Management.pdf p.6</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2790,7 +2793,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>10.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -2824,12 +2827,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>The risk weight for unsecured consumer loans (excluding housing loans, educational loans, vehicle loans, loans against gold jewellery, and microfinance/SHG loans) is 125% [1], as specified under Sr. No. (e)(i) in the Risk Weight Assets (RWAs) guidelines. This applies to retail loans categorized as consumer credit exposure.</t>
+          <t>The risk weight for unsecured consumer loans (classified as retail loans excluding housing loans, educational loans, vehicle loans, loans against gold jewellery, and microfinance/SHG loans) is 125% [4].</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>12959_Prudential-Norms-on-Capital-Adequacy.pdf p.22 | 12953_Concentration-Risk-Management.pdf p.14 | 12953_Concentration-Risk-Management.pdf p.10 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.22 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.26 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.26</t>
+          <t>12953_Concentration-Risk-Management.pdf p.10 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.22 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.44 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.22 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.26 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.21</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2843,7 +2846,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -2877,12 +2880,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>The ₹6 crore loan to a director's relative falls under the materiality threshold for a Middle Layer NBFC. According to [2], the materiality threshold for Middle Layer NBFCs is ₹5 crore. Since the loan exceeds this threshold, it must be sanctioned by the Board of the NBFC. Additionally, the director's relative is classified as a "related party" under [5], further subjecting the loan to the defined thresholds and governance requirements. The loan is not eligible for exemption under sub-clause (xii) of [1], as it pertains to specific deposit instruments, not loans.</t>
+          <t>The ₹6 crore loan to a director's relative (a "related party") falls under the materiality threshold rules for Middle Layer NBFCs. According to [3], the materiality threshold for Middle Layer NBFCs is ₹5 crore. Since the loan exceeds this threshold, it must be sanctioned by the Board of the NBFC [3]. Additionally, the relative is classified as a "related party" under [5], which defines relatives of directors as included in the related party framework. The loan is also subject to credit risk management regulations applicable to Middle Layer NBFCs, as outlined in the Directions [2][4].</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>12958_Acceptance-of-Public-Deposits.pdf p.8 | 12954_Credit-Risk-Management.pdf p.13 | 12953_Concentration-Risk-Management.pdf p.2 | 12941_Managing-Risks-in-Outsourcing.pdf p.4 | 12954_Credit-Risk-Management.pdf p.6 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.26</t>
+          <t>12958_Acceptance-of-Public-Deposits.pdf p.8 | 12953_Concentration-Risk-Management.pdf p.2 | 12954_Credit-Risk-Management.pdf p.13 | 12941_Managing-Risks-in-Outsourcing.pdf p.4 | 12954_Credit-Risk-Management.pdf p.6 | 12931_Miscellaneous.pdf p.2</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2896,7 +2899,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
@@ -2930,22 +2933,20 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>The key rules for a Middle Layer NBFC entering co-lending with a bank are:  
-1. Co-lending arrangements must comply with the **Reserve Bank of India (Non-Banking Financial Companies - Transfer and Distribution of Credit Risk) Directions, 2025** [1].  
-2. The **Commitment Letter Agreement (CLA)** must ensure:  
-   - Partner REs (lenders) irrevocably commit to take their share of loans on a back-to-back basis [2].  
-   - Shares are reflected in the books of both REs within **15 calendar days** of disbursement [2].  
-   - Loans under CLA are included in internal/statutory audits [2].  
-3. NBFCs must retain a **minimum 10% share** of individual loans in their books under CLA [4].  
-4. **No third party** (including LSPs) may have direct or indirect control over fund flows in co-lending transactions [1].  
-5. The CLA agreement must detail segregation of responsibilities, customer interface, and grievance redressal mechanisms [4].  
-6. **Digital lending disclosures** (e.g., KFS, digitally signed documents) must be provided to borrowers as per RBI guidelines [1].  
-7. **CRAR and NPA thresholds** must be met for eligibility in co-lending, as per prudential norms [5].</t>
+          <t>- Co-lending arrangements must comply with the Reserve Bank of India (Non-Banking Financial Companies - Transfer and Distribution of Credit Risk) Directions, 2025 [1].  
+- No third party (other than lenders in the co-lending transaction) may have direct or indirect control over fund flows [1].  
+- The originating NBFC must transfer the loan share to the partner RE under CLA only as per the ex-ante agreement and KFS, within 15 calendar days of disbursement; otherwise, the loan remains on the originating NBFC’s books [2].  
+- NBFCs under CLA must retain a minimum 10% share of individual loans in their books [4].  
+- The CLA agreement must specify borrower selection criteria, product lines, fees, segregation of responsibilities, and grievance redressal mechanisms [4].  
+- Loans under CLA must be included in internal/statutory audits [2].  
+- NBFCs must ensure digital lending products, DLAs, and LSP details are publicly accessible on their websites [1].  
+- Disbursement must be directly into the borrower’s bank account, except for statutory mandates or co-lending (where funds must flow directly to the end-beneficiary) [1].  
+- Compliance with KYC norms and fair practice codes is mandatory [2].</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>12957_Credit-Facilities.pdf p.15 | 12952_Transfer-and-Distribution-of-Credit-Risk.pdf p.37 | 12961_Undertaking-of-Financial-Services.pdf p.13 | 12952_Transfer-and-Distribution-of-Credit-Risk.pdf p.35 | 12934_Peer-to-Peer-Lending-Platform.pdf p.11 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.12</t>
+          <t>12957_Credit-Facilities.pdf p.15 | 12952_Transfer-and-Distribution-of-Credit-Risk.pdf p.37 | 12961_Undertaking-of-Financial-Services.pdf p.13 | 12952_Transfer-and-Distribution-of-Credit-Risk.pdf p.35 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13 | 12946_Wilful-Defaulters-and-Large-Defaulters.pdf p.3</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2959,7 +2960,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -2993,23 +2994,23 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>The conditions applicable to a Middle Layer NBFC onboarding customers via video KYC (V-CIP or non-face-to-face mode) include:  
-- **Verification of identity**: The NBFC must ensure the customer’s photograph in Aadhaar/OVD matches the one in PAN/e-PAN, and details in Aadhaar/OVD and PAN/e-PAN match the customer’s provided information [2(27)(xiii)].  
-- **Transaction restrictions**: Alternate mobile numbers cannot be linked post-CDD; transactions must be routed through the mobile number used for account opening. A Board-approved policy must govern mobile number changes [5(44)(2)].  
-- **Address verification**: Current address must be verified via positive confirmation (e.g., address verification letter, contact point verification) before allowing account operations [5(44)(3)].  
-- **Digital KYC process**: The authorized officer must declare live photo capture and verify with OTP; the officer’s live photo must also be captured. The CAF (Customer Application Form) must be digitally signed, with customer signatures/thumb impressions, and uploaded to the system [3(24)(10)-(13)].  
-- **Account limits**:  
-  - Aggregate balance of deposit accounts cannot exceed ₹1 lakh; exceeding this suspends operations until CDD is completed [3(25)(3)].  
-  - Annual credit limit across all deposit accounts is ₹2 lakh [3(25)(4)].  
-  - Borrowal accounts (term loans) are limited to ₹60,000 annually [3(25)(5)].  
-- **Periodic updation**: KYC records must be updated to current CDD standards during periodic updation, with acknowledgment provided to customers [1(42)(5)(8)].  
-- **CDD requirements**: Accounts opened via OTP-based e-KYC must undergo CDD as per paragraph 23 or 26-27 (V-CIP) within one year; failure to do so results in account closure or restricted debits [3(25)(6)-(7)].  
-- **KYC Identifier**: The NBFC must retrieve KYC Identifier from CKYCR for onboarding/updation, avoiding redundant document submission unless there is a change in customer information, incomplete records, expired documents, or enhanced due diligence needs [6(7)(i)-(iv)].</t>
+          <t>The conditions for onboarding customers via video KYC (V-CIP) include:  
+- Ensuring the customer’s photograph in Aadhaar/ODV matches the one during V-CIP, and identification details in Aadhaar/ODV and PAN/e-PAN align with the customer’s provided details [2].  
+- Conducting a concurrent audit to operationalize accounts opened via V-CIP [2].  
+- Storing V-CIP data and recordings in India, securely with timestamps for historical reference [2].  
+- Preserving activity logs of the V-CIP process with credentials of the official performing it [2].  
+- For new customers, verifying PAN details from the issuing authority during periodic KYC updates [1].  
+- Adhering to balance and credit limits: aggregate deposit balances ≤ ₹1 lakh, aggregate credits ≤ ₹2 lakh annually, and term loans ≤ ₹60,000 for borrowal accounts [3].  
+- Closing accounts if balances exceed thresholds without completing CDD [3].  
+- Ensuring periodic KYC updates follow risk-based approaches and internal policies approved by the Board [1].  
+- Avoiding accounts in fictitious names and applying CDD for all joint account holders [4].  
+- Verifying PAN, GST, and digital signatures as per statutory requirements [4].  
+- Not allowing other REs to use KYC data from OTP-based accounts without fresh authentication [3].</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>12943_Know-Your-Customer.pdf p.42 | 12943_Know-Your-Customer.pdf p.34 | 12943_Know-Your-Customer.pdf p.28 | 12943_Know-Your-Customer.pdf p.19 | 12943_Know-Your-Customer.pdf p.45 | 12943_Know-Your-Customer.pdf p.56</t>
+          <t>12943_Know-Your-Customer.pdf p.42 | 12943_Know-Your-Customer.pdf p.34 | 12943_Know-Your-Customer.pdf p.28 | 12943_Know-Your-Customer.pdf p.19 | 12943_Know-Your-Customer.pdf p.30 | 12961_Undertaking-of-Financial-Services.pdf p.23</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3023,7 +3024,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>18.4</v>
+        <v>10.5</v>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
@@ -3057,14 +3058,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>For a Middle Layer NBFC with over ₹1,000 crore assets, the statutory auditor rules are as follows:  
-1. **Branch Audit Requirements**: The NBFC must audit at least the top 20 branches (or top 20% of branches if fewer than 100) based on outstanding advances, ensuring coverage of at least 15% of total gross advances. Additionally, adherence to Section 143(8) of the Companies Act, 2013, for branch audit compliance is mandatory [1].  
-2. **Auditor Eligibility Criteria**:  
-   - For asset sizes **above ₹15,000 crore**, the audit firm must have a minimum of 5 full-time partners (FTPs), 4 FCA partners, 2 CISA/ISA qualified professionals, 15 years of audit experience, and 18 professional staff [6].  
-   - For asset sizes **above ₹1,000 crore but below ₹15,000 crore**, the requirements include 3 FTPs, 2 FCA partners, 1 CISA/ISA qualified professional, 8 years of audit experience, and 12 professional staff [6].  
-3. **Joint Audit Requirement**: If the NBFC’s asset size exceeds ₹15,000 crore, statutory audits must be conducted under joint audit by **a minimum of two audit firms** with no common partners or shared audit networks [1].  
-4. **Audit Firm Allocation**: The NBFC must finalize work allocation among SCAs/SAs in consultation with them before audit commencement [1].  
-These rules apply to Middle Layer NBFCs as defined in the context, with specific thresholds based on asset size.</t>
+          <t>For a Middle Layer NBFC with over ₹1,000 crore in assets, the statutory auditor rules are as follows:  
+- **Audit Firm Requirements**: The NBFC must appoint audit firms meeting eligibility criteria based on its asset size. For asset sizes **above ₹1,000 crore and up to ₹15,000 crore**, the audit firm must have:  
+  - Minimum **3 full-time partners (FTPs)** with at least 3 years of association [6].  
+  - Minimum **2 Fellow Chartered Accountant (FCA) partners** among the FTPs [6].  
+  - Minimum **1 Full Time Partner/Paid CA with CISA/ISA qualification** [6].  
+  - Minimum **8 years of audit experience** for the firm [6].  
+  - Minimum **12 professional staff** [6].  
+- **Annual Certification**: Statutory auditors must certify the NBFC’s asset size (as of March 31) annually and submit it to the Reserve Bank’s Department of Supervision [3].  
+- **Branch Audit Coverage**: The NBFC must audit at least the top 20 branches (or top 20% of branches if fewer than 100) based on outstanding advances, covering a minimum of 15% of total gross advances [1].  
+- **Joint Audit**: If the NBFC’s asset size exceeds ₹15,000 crore, it must conduct statutory audits under joint audit by **minimum two audit firms** with no common partners or shared audit networks [1].  
+These rules apply to NBFCs in the Middle Layer category, which includes those with asset sizes of ₹1,000 crore or more [2].</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3083,7 +3087,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>24.9</v>
+        <v>17.3</v>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -3117,12 +3121,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>The borrower's account is classified as **SMA-2** since it is 65 days overdue. According to paragraph 19 of [1], SMA-2 applies to accounts overdue for more than 60 days but up to 90 days. For Middle Layer NBFCs, NPA classification requires overdue periods exceeding 90 days [4]. Thus, the account remains a special mention account (SMA-2) until it reaches 90 days overdue.</t>
+          <t>The borrower's 65-day overdue status classifies it as **SMA-2** (Special Mention Account-2), as per the criteria in paragraph 18 of [6], which defines SMA-2 as overdue between 60 and 90 days. This applies regardless of the NBFC's layer, as SMA classification is mandated for all loans [19]. Since 65 days falls within the SMA-2 range, it is not yet a non-performing asset (NPA), which requires overdue periods exceeding 90 days [1, 4].</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.7 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.20 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.17 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.12 | 12947_Resolution-of-Stressed-Assets.pdf p.14</t>
+          <t>12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.20 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.7 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.17 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.12 | 12947_Resolution-of-Stressed-Assets.pdf p.14</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3136,7 +3140,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>8.699999999999999</v>
+        <v>19.1</v>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
@@ -3170,21 +3174,20 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>For a Middle Layer NBFC moving its loan management system to a cloud vendor, the following apply:  
-- **Chapter IV** and **IT-specific provisions in Chapter II** of the Directions are applicable [1](#1).  
-- **Cloud-specific requirements** include:  
-  - A comprehensive assessment of business strategy, cloud-related expenditures, and risk management frameworks [2](#2).  
-  - Ensuring the **IT outsourcing policy** covers the entire data lifecycle (generation to deletion) and aligns with legal/regulatory requirements [2](#2).  
-  - Implementing **cloud security best practices** (e.g., shared responsibility model, NIST SP 800-210) and controls for data integrity, confidentiality, and resilience [2](#2)[4](#4).  
-  - Establishing **cloud governance** with documented policies, data sovereignty compliance, and stakeholder protection [2](#2).  
-  - Conducting **due diligence** on CSPs, ensuring contracts address data storage, protection, and enforceability [4](#4).  
-  - Defining **monitoring requirements**, assessing CSP’s cybersecurity capabilities, and ensuring subcontractor safeguards [4](#4).  
-These requirements are in addition to general outsourcing provisions in **Chapter III** [1](#1).</t>
+          <t>For a Middle Layer NBFC migrating its loan management system to a cloud vendor, the applicable provisions are:  
+- **Chapter III** of the Directions applies to material outsourcing arrangements, including cloud services [1]. This includes requirements for assessing business strategy, IT outsourcing policies, and risk management frameworks [3].  
+- **IT-specific provisions in Chapter II** (e.g., Board-level IT outsourcing policy) apply to Middle Layer NBFCs and above [1].  
+- **F.4 Usage of Cloud Computing Services** mandates specific controls, such as:  
+  - Comprehensive risk assessment of cloud adoption and data lifecycle management [3].  
+  - Cloud governance policies, including due diligence of CSPs, secure architecture, identity/access management (IAM), and integration with SOC [3-4].  
+  - Security controls aligned with NIST SP 800-210, encryption, data sovereignty, and multi-tenancy safeguards [3-4].  
+- **Exemptions**: NBFC-P2P, NBFC-AA, CICs, and NOFHCs are excluded [1][2][5].  
+These requirements ensure compliance with regulatory frameworks for cloud migration and outsourcing.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>12941_Managing-Risks-in-Outsourcing.pdf p.4 | 12941_Managing-Risks-in-Outsourcing.pdf p.39 | 12953_Concentration-Risk-Management.pdf p.2 | 12941_Managing-Risks-in-Outsourcing.pdf p.41 | 12957_Credit-Facilities.pdf p.15 | 12961_Undertaking-of-Financial-Services.pdf p.2</t>
+          <t>12941_Managing-Risks-in-Outsourcing.pdf p.4 | 12953_Concentration-Risk-Management.pdf p.2 | 12941_Managing-Risks-in-Outsourcing.pdf p.39 | 12941_Managing-Risks-in-Outsourcing.pdf p.41 | 12961_Undertaking-of-Financial-Services.pdf p.2 | 12957_Credit-Facilities.pdf p.15</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3198,7 +3201,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>9.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
@@ -3232,26 +3235,26 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>The provided context passages do not specify SEBI LODR disclosure timelines for listed NCDs.</t>
+          <t>The provided context passages do not specify SEBI LODR disclosure timelines for listed NCDs. The references to SEBI LODR in the passages relate to corporate governance disclosures [2] and currency futures disclosures [5], but none address timelines for NCD-specific disclosures.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>12938_Standalone-Primary-Dealers.pdf p.47 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.37 | 12947_Resolution-of-Stressed-Assets.pdf p.49 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.29 | 12939_Housing-Finance-Companies.pdf p.82 | 12931_Miscellaneous.pdf p.6</t>
+          <t>12938_Standalone-Primary-Dealers.pdf p.47 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.37 | 12947_Resolution-of-Stressed-Assets.pdf p.49 | 12931_Miscellaneous.pdf p.5 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.29 | 12939_Housing-Finance-Companies.pdf p.82</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>answered a question the corpus should not cover - check for invention</t>
+          <t>correctly declined to answer</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
@@ -3285,26 +3288,26 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>The provided context passages do not specify SEBI's requirements for a debenture trustee in a public NCD issue.</t>
+          <t>The provided context passages do not specify SEBI's requirements for a debenture trustee in relation to public NCD issues.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>12938_Standalone-Primary-Dealers.pdf p.47 | 13585_SUP-Auditors-Report.pdf p.4 | 12931_Miscellaneous.pdf p.6 | 12938_Standalone-Primary-Dealers.pdf p.43 | 12937_Core-Investment-Companies.pdf p.2 | 12947_Resolution-of-Stressed-Assets.pdf p.49</t>
+          <t>12938_Standalone-Primary-Dealers.pdf p.47 | 13585_SUP-Auditors-Report.pdf p.4 | 12931_Miscellaneous.pdf p.5 | 12938_Standalone-Primary-Dealers.pdf p.43 | 12943_Know-Your-Customer.pdf p.72 | 12947_Resolution-of-Stressed-Assets.pdf p.49</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>answered a question the corpus should not cover - check for invention</t>
+          <t>correctly declined to answer</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
@@ -3338,7 +3341,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>The provided context passages do not specify a numerical limit on the number of insurers an IRDAI corporate agent can tie up with. The regulations focus on compliance requirements, such as avoiding restrictive practices [1][3], adhering to IRDA guidelines [5], and ensuring voluntary customer choice. No explicit cap on the number of insurers is mentioned.</t>
+          <t>The context passages do not specify a maximum number of insurers that an IRDAI corporate agent can tie up with. The relevant sections (e.g., [1][3][5]) outline conditions for acting as a corporate agent, such as obtaining IRDAI permission, avoiding restrictive practices, and ensuring voluntary customer choice, but none mention a numerical limit on the number of insurers. Thus, the answer cannot be determined from the provided passages.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3348,16 +3351,16 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>answered a question the corpus should not cover - check for invention</t>
+          <t>correctly declined to answer</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
@@ -3391,26 +3394,26 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>The provided context passages do not mention anything about the TDS (Tax Deducted at Source) threshold on interest paid to depositors.</t>
+          <t>The provided context passages do not mention the TDS (Tax Deducted at Source) threshold on interest paid to depositors.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>12958_Acceptance-of-Public-Deposits.pdf p.37 | 12949_Asset-Liability-Management.pdf p.40 | 12958_Acceptance-of-Public-Deposits.pdf p.43 | 12958_Acceptance-of-Public-Deposits.pdf p.14 | 12958_Acceptance-of-Public-Deposits.pdf p.20 | 12958_Acceptance-of-Public-Deposits.pdf p.4</t>
+          <t>12958_Acceptance-of-Public-Deposits.pdf p.37 | 12949_Asset-Liability-Management.pdf p.40 | 12958_Acceptance-of-Public-Deposits.pdf p.14 | 12958_Acceptance-of-Public-Deposits.pdf p.20 | 12958_Acceptance-of-Public-Deposits.pdf p.4 | 12949_Asset-Liability-Management.pdf p.41</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>answered a question the corpus should not cover - check for invention</t>
+          <t>correctly declined to answer</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
@@ -3444,26 +3447,26 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>The provided context passages do not specify the exact GST rate applicable to loan processing fees. They only mention that NBFCs must comply with CBIC instructions regarding GST on penal charges [4], and that fees/charges may be disclosed net of taxes such as GST [1][2]. No specific GST rate is provided in the text.</t>
+          <t>The context passages do not specify the exact GST rate applicable to loan processing fees. However, they mention that NBFCs must follow instructions from the Central Board of Indirect Taxes &amp; Customs (CBIC) regarding the applicability of GST on penal charges [1]. For loan processing fees, the GST treatment would depend on CBIC's clarifications, but no specific rate is provided in the given texts.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>12942_Responsible-Business-Conduct.pdf p.35 | 12942_Responsible-Business-Conduct.pdf p.35 | 12942_Responsible-Business-Conduct.pdf p.35 | 12942_Responsible-Business-Conduct.pdf p.14 | 12939_Housing-Finance-Companies.pdf p.53 | 12942_Responsible-Business-Conduct.pdf p.4</t>
+          <t>12942_Responsible-Business-Conduct.pdf p.14 | 12939_Housing-Finance-Companies.pdf p.53 | 12956_Credit-Cards-Issuance-and-Conduct.pdf p.13 | 12942_Responsible-Business-Conduct.pdf p.4 | 12952_Transfer-and-Distribution-of-Credit-Risk.pdf p.36 | 12942_Responsible-Business-Conduct.pdf p.12</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>answered a question the corpus should not cover - check for invention</t>
+          <t>correctly declined to answer</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
@@ -3497,26 +3500,26 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>The provided context passages do not mention any requirement to allocate 2% of profits to CSR (Corporate Social Responsibility). The documents focus on regulatory guidelines for NBFCs, dividend payout ratios, capital adequacy, exposure norms, and asset classification, but none reference CSR obligations or profit allocation percentages for such purposes.</t>
+          <t>The provided context passages do not mention any requirement to allocate 2% of profits to CSR (Corporate Social Responsibility). The content focuses on dividend payout ratios, capital adequacy norms, risk management, and regulatory definitions, but no reference to CSR obligations or profit allocation percentages is present.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>12944_Declaration-of-Dividends.pdf p.6 | 12935_Mortgage-Guarantee-Companies.pdf p.8 | 12938_Standalone-Primary-Dealers.pdf p.3 | 12964_Acquisition-of-Shareholding-or-Control.pdf p.11 | 12947_Resolution-of-Stressed-Assets.pdf p.35 | 12953_Concentration-Risk-Management.pdf p.10</t>
+          <t>12944_Declaration-of-Dividends.pdf p.6 | 12938_Standalone-Primary-Dealers.pdf p.3 | 12964_Acquisition-of-Shareholding-or-Control.pdf p.11 | 12953_Concentration-Risk-Management.pdf p.10 | 12947_Resolution-of-Stressed-Assets.pdf p.35 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.22</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>answered a question the corpus should not cover - check for invention</t>
+          <t>correctly declined to answer</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
@@ -3550,7 +3553,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>The context passages do not specify the deadline for holding the annual general meeting.</t>
+          <t>The context passages do not specify a deadline for holding the annual general meeting. They only mention that certain documents must be submitted to regulatory authorities within fifteen days of the meeting [1][2]. No explicit deadline for the meeting itself is provided in the text.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3560,16 +3563,16 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>answered a question the corpus should not cover - check for invention</t>
+          <t>correctly declined to answer</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
@@ -3603,12 +3606,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>The provided context passages do not contain information about trading windows for insiders or deadlines related to results.</t>
+          <t>The provided context passages do not contain any information regarding trading windows for insiders or timelines related to results announcements.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>12949_Asset-Liability-Management.pdf p.10 | 12938_Standalone-Primary-Dealers.pdf p.51 | 12949_Asset-Liability-Management.pdf p.38 | 12938_Standalone-Primary-Dealers.pdf p.54 | 12949_Asset-Liability-Management.pdf p.14 | 12949_Asset-Liability-Management.pdf p.36</t>
+          <t>12949_Asset-Liability-Management.pdf p.10 | 12938_Standalone-Primary-Dealers.pdf p.51 | 12938_Standalone-Primary-Dealers.pdf p.54 | 12949_Asset-Liability-Management.pdf p.38 | 12955_Credit-Information-Reporting.pdf p.32 | 12949_Asset-Liability-Management.pdf p.14</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3622,7 +3625,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
@@ -3656,12 +3659,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>The provided context passages do not contain any information regarding commissions earned on group credit-life insurance sold with loans.</t>
+          <t>The provided context passages do not mention any commission rates or earnings related to group credit-life insurance sold with loans. The documents focus on regulatory definitions, data reporting requirements, and insurance business eligibility criteria for CICs, but none address financial commissions for such products.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>12955_Credit-Information-Reporting.pdf p.55 | 12955_Credit-Information-Reporting.pdf p.10 | 12952_Transfer-and-Distribution-of-Credit-Risk.pdf p.6 | 12942_Responsible-Business-Conduct.pdf p.35 | 12961_Undertaking-of-Financial-Services.pdf p.16 | 12955_Credit-Information-Reporting.pdf p.62</t>
+          <t>12955_Credit-Information-Reporting.pdf p.55 | 12952_Transfer-and-Distribution-of-Credit-Risk.pdf p.6 | 12955_Credit-Information-Reporting.pdf p.65 | 12955_Credit-Information-Reporting.pdf p.62 | 12961_Undertaking-of-Financial-Services.pdf p.16 | 12955_Credit-Information-Reporting.pdf p.10</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3675,7 +3678,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
@@ -3709,12 +3712,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>The provided context passages do not contain information regarding tax deductions for NPA provisions. They focus on provisioning norms, impairment allowances, regulatory compliance, and asset classification under RBI directions and IndAS, but none address tax treatment or deductibility.</t>
+          <t>The provided context passages do not address tax deductibility of NPA provisions. They focus on accounting treatment, provisioning calculations, and asset classification rules under prudential norms, but do not mention tax implications or deductions related to NPAs.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.12 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.10 | 12949_Asset-Liability-Management.pdf p.29 | 12947_Resolution-of-Stressed-Assets.pdf p.57 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.44 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.14</t>
+          <t>12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.12 | 12949_Asset-Liability-Management.pdf p.29 | 12947_Resolution-of-Stressed-Assets.pdf p.57 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.44 | 12947_Resolution-of-Stressed-Assets.pdf p.35 | 12947_Resolution-of-Stressed-Assets.pdf p.15</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3728,7 +3731,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>

--- a/eval/nbfc_retrieval_test_questions_results.xlsx
+++ b/eval/nbfc_retrieval_test_questions_results.xlsx
@@ -511,12 +511,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>The asset-size threshold for a non-deposit-taking NBFC to be placed in the Middle Layer is ₹1,000 crore. This is explicitly stated in [1], which includes non-deposit taking NBFCs with asset size of ₹1,000 crore and above in the Middle Layer. Additionally, [2] confirms that once an NBFC reaches ₹1,000 crore, it is subject to Middle Layer regulations. [3] further supports this by noting that existing NBFC-ND-SI with asset size ₹500 crore and above but below ₹1,000 crore are classified as Base Layer, implying ₹1,000 crore as the threshold for Middle Layer.</t>
+          <t>The asset-size threshold for a non-deposit-taking NBFC to be placed in the Middle Layer is ₹1,000 crore. This is explicitly stated in [1], which includes non-deposit taking NBFCs with asset size of ₹1,000 crore and above in the Middle Layer. Additionally, [2] confirms that once an NBFC reaches this threshold, it is subject to Middle Layer regulatory requirements.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.10 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.11 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.12 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13 | 13592_SUP-Cybersecurity-Technology-Risk-Resilience.pdf p.3</t>
+          <t>12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.10 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.11 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.12 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13 | 13590_SUP-Fraud-Risk-Management.pdf p.4</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>7.3</v>
+        <v>12.6</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -564,7 +564,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>The minimum CRAR for a Middle Layer NBFC is 15 per cent of the aggregate RWAs [1]. Of this, the minimum Tier 1 capital required is 10 per cent of the aggregate RWAs [1].</t>
+          <t>The minimum CRAR for a Middle Layer NBFC is 15% of aggregate RWAs [1], and the minimum Tier 1 capital required is 10% of aggregate RWAs [1].</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>7</v>
+        <v>11.3</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -622,7 +622,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>12959_Prudential-Norms-on-Capital-Adequacy.pdf p.7 | 12953_Concentration-Risk-Management.pdf p.10 | 12933_Microfinance-Institution.pdf p.9 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.7 | 12944_Declaration-of-Dividends.pdf p.6 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.22</t>
+          <t>12959_Prudential-Norms-on-Capital-Adequacy.pdf p.7 | 12953_Concentration-Risk-Management.pdf p.10 | 12933_Microfinance-Institution.pdf p.9 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.7 | 12944_Declaration-of-Dividends.pdf p.6 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.12</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -670,12 +670,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>The minimum Net Owned Fund (NOF) required for an NBFC-ICC is ₹10 crore, which must be achieved by March 31, 2027 [2]. Existing NBFC-ICC entities currently have a NOF of ₹2 crore and must progressively increase it to ₹5 crore by March 31, 2025, and ₹10 crore by March 31, 2027 [2].</t>
+          <t>The minimum Net Owned Fund (NOF) required for an NBFC-ICC is ₹10 crore, which must be achieved by March 31, 2027 [2]. Existing NBFC-ICC currently have a NOF of ₹2 crore and must incrementally reach ₹5 crore by March 31, 2025, and ₹10 crore by March 31, 2027 [2].</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>12939_Housing-Finance-Companies.pdf p.13 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.21 | 12936_Account-Aggregator.pdf p.8 | 12934_Peer-to-Peer-Lending-Platform.pdf p.5 | 12939_Housing-Finance-Companies.pdf p.8 | 12961_Undertaking-of-Financial-Services.pdf p.13</t>
+          <t>12939_Housing-Finance-Companies.pdf p.13 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.21 | 12936_Account-Aggregator.pdf p.8 | 12934_Peer-to-Peer-Lending-Platform.pdf p.5 | 12939_Housing-Finance-Companies.pdf p.8 | 12931_Miscellaneous.pdf p.17</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>10.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -723,12 +723,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>The minimum NOF for NBFC-P2P is ₹2 crore [1] and for NBFC-AA is also ₹2 crore [1].</t>
+          <t>The minimum NOF for NBFC-P2P is ₹2 crore [1]§40, and for NBFC-AA, it is also ₹2 crore [1]§40.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.21 | 12961_Undertaking-of-Financial-Services.pdf p.25 | 12931_Miscellaneous.pdf p.17 | 12934_Peer-to-Peer-Lending-Platform.pdf p.10 | 12939_Housing-Finance-Companies.pdf p.13 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.2</t>
+          <t>12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.21 | 12961_Undertaking-of-Financial-Services.pdf p.25 | 12931_Miscellaneous.pdf p.17 | 12934_Peer-to-Peer-Lending-Platform.pdf p.10 | 12939_Housing-Finance-Companies.pdf p.13 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.10</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -776,7 +776,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>After the glide path ended (March 31, 2026), the NPA classification for NBFCs follows the 90-day overdue threshold. This is specified in the glide path timeline for applicable NBFCs [1], which transitions them to the 90-day norm upon completion of the glide path. For Base Layer NBFCs, the NPA classification is triggered by an overdue period of **more than 90 days** [1].</t>
+          <t>After the glide path ended (March 31, 2026), the NPA classification for a Base Layer NBFC is triggered by an overdue period of **more than 90 days** [1]. This applies to NBFCs transitioning to the 90-day NPA norm as per the glide path timeline [1].</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>The provisioning requirement for sub-standard assets is a general provision of **10 per cent of total outstanding** [4], and this rate is also explicitly stated in the provisioning norms for NPAs under paragraph 32(1) of the 2025 Directions [5].</t>
+          <t>The provisioning requirement for sub-standard assets is a general provision of **10 per cent of total outstanding**. This is specified in [4] for mortgage guarantee assets and in [5] for NBFCs.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7.7</v>
+        <v>11.2</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -882,7 +882,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>The standard asset provisioning rate for Middle Layer NBFCs (NBFC-ML) is 0.40 per cent of the outstanding amount, as specified in paragraph 55 of the RBI directions [1]. This rate also applies to microfinance loans [1].</t>
+          <t>The standard asset provisioning rate for Middle Layer NBFCs (NBFC-ML) is 0.40 per cent of the outstanding amount, as specified in paragraph 55 of the Reserve Bank of India (Non-Banking Financial Companies - Income Recognition, Asset Classification and Provisioning) Directions, 2025 [1]. This rate applies to standard assets, including microfinance loans [1].</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -935,26 +935,26 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>High-risk customers require periodic KYC updation at least once every two years, medium-risk customers once every eight years, and low-risk customers once every 10 years [1].</t>
+          <t>The NBFC must periodically update KYC for high-risk customers every 2 years, medium-risk customers every 8 years, and low-risk customers every 10 years from the date of account opening or last KYC updation [1].</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>12943_Know-Your-Customer.pdf p.41 | 12943_Know-Your-Customer.pdf p.57 | 12943_Know-Your-Customer.pdf p.42 | 12943_Know-Your-Customer.pdf p.44 | 12943_Know-Your-Customer.pdf p.34 | 12943_Know-Your-Customer.pdf p.15</t>
+          <t>12943_Know-Your-Customer.pdf p.41 | 12943_Know-Your-Customer.pdf p.57 | 12943_Know-Your-Customer.pdf p.42 | 12943_Know-Your-Customer.pdf p.44 | 12943_Know-Your-Customer.pdf p.15 | 12943_Know-Your-Customer.pdf p.6</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CHECK</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>found 10years; missing 2years, 8years</t>
+          <t>all key figures present (2years, 8years, 10years)</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -988,12 +988,15 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Customer identification and transaction records must be preserved for at least five years from the date of the transaction [1], and records pertaining to customer identification (including addresses) must be preserved for five years after the business relationship has ended [1]. For non-profit organization customers, registration details must be maintained for five years after the business relationship ends or the account is closed, whichever is later [1].</t>
+          <t>Customer identification and transaction records must be preserved as follows:  
+- Transaction records must be maintained for **at least five years from the date of the transaction** [1].  
+- Records pertaining to customer identification and addresses (obtained during account opening or business relationship) must be preserved for **at least five years after the business relationship has ended** [1].  
+These requirements are explicitly outlined in Chapter VII, Section 47 of the provided context.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>12943_Know-Your-Customer.pdf p.48 | 12943_Know-Your-Customer.pdf p.34 | 12943_Know-Your-Customer.pdf p.44 | 12943_Know-Your-Customer.pdf p.22 | 12943_Know-Your-Customer.pdf p.57 | 12957_Credit-Facilities.pdf p.20</t>
+          <t>12943_Know-Your-Customer.pdf p.48 | 12943_Know-Your-Customer.pdf p.34 | 12943_Know-Your-Customer.pdf p.44 | 12943_Know-Your-Customer.pdf p.7 | 12943_Know-Your-Customer.pdf p.22 | 12943_Know-Your-Customer.pdf p.57</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1007,7 +1010,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1041,12 +1044,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>The context passages do not specify a particular timeline for filing Suspicious Transaction Reports (STRs) with FIU-IND. While passage [1] mentions that delays in reporting constitute violations [1], it does not define the exact time limit. Other sections reference reporting obligations but do not explicitly state a timeframe for STR filings.</t>
+          <t>The context passages do not specify a particular timeline for filing a Suspicious Transaction Report (STR) with FIU-IND. However, they emphasize that delays in reporting are violations [1], and entities must file STRs promptly upon detecting suspicious transactions, in accordance with PML Rules [3]. No exact number of days is provided for the filing deadline.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>12943_Know-Your-Customer.pdf p.50 | 12943_Know-Your-Customer.pdf p.72 | 12943_Know-Your-Customer.pdf p.63 | 12941_Managing-Risks-in-Outsourcing.pdf p.13 | 12939_Housing-Finance-Companies.pdf p.83 | 12943_Know-Your-Customer.pdf p.60</t>
+          <t>12943_Know-Your-Customer.pdf p.50 | 12943_Know-Your-Customer.pdf p.72 | 12943_Know-Your-Customer.pdf p.63 | 12939_Housing-Finance-Companies.pdf p.83 | 13587_SUP-Supervisory-Returns.pdf p.12 | 12955_Credit-Information-Reporting.pdf p.7</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1060,7 +1063,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>8.4</v>
+        <v>11.2</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1094,12 +1097,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>The minimum tenure for public deposits accepted by an NBFC is twelve months, and the maximum is sixty months from the date of acceptance or renewal [4].</t>
+          <t>The minimum tenure for public deposits accepted by an NBFC is twelve months, and the maximum is sixty months from the date of acceptance or renewal [5].</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>12958_Acceptance-of-Public-Deposits.pdf p.13 | 12931_Miscellaneous.pdf p.5 | 12958_Acceptance-of-Public-Deposits.pdf p.13 | 12958_Acceptance-of-Public-Deposits.pdf p.13 | 12958_Acceptance-of-Public-Deposits.pdf p.18 | 12958_Acceptance-of-Public-Deposits.pdf p.22</t>
+          <t>12958_Acceptance-of-Public-Deposits.pdf p.13 | 12931_Miscellaneous.pdf p.5 | 13585_SUP-Auditors-Report.pdf p.4 | 12958_Acceptance-of-Public-Deposits.pdf p.13 | 12958_Acceptance-of-Public-Deposits.pdf p.13 | 12958_Acceptance-of-Public-Deposits.pdf p.18</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1147,7 +1150,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>The ceiling on public deposits an NBFC-D can hold relative to its NOF is **one and one-half times** its NOF [1].</t>
+          <t>The ceiling on public deposits an NBFC-D can hold relative to its NOF is **one and one-half times** its NOF. This is stipulated in [1], which states that an NBFC shall accept or renew public deposits not exceeding one and one-half times its NOF.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1166,7 +1169,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -1200,12 +1203,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>The percentage of public deposits that an NBFC-D must maintain in liquid assets is **15%**. This is specified in paragraph 10 of Chapter-II of the Directions, which requires NBFC-Ds to invest in unencumbered approved securities valued at not less than 15% of the public deposits outstanding [1].</t>
+          <t>The NBFC-D must maintain **15 per cent** of public deposits in liquid assets, as specified in Chapter-II Requirement of Maintenance of Liquid Assets [1]. This includes investments in unencumbered approved securities and other specified instruments, with the aggregate not falling below 15 per cent of public deposits.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>12958_Acceptance-of-Public-Deposits.pdf p.12 | 12939_Housing-Finance-Companies.pdf p.8 | 12949_Asset-Liability-Management.pdf p.20 | 12958_Acceptance-of-Public-Deposits.pdf p.2 | 12939_Housing-Finance-Companies.pdf p.38 | 12958_Acceptance-of-Public-Deposits.pdf p.26</t>
+          <t>12958_Acceptance-of-Public-Deposits.pdf p.12 | 12939_Housing-Finance-Companies.pdf p.8 | 12949_Asset-Liability-Management.pdf p.20 | 12939_Housing-Finance-Companies.pdf p.38 | 12958_Acceptance-of-Public-Deposits.pdf p.26 | 12958_Acceptance-of-Public-Deposits.pdf p.28</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1219,7 +1222,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -1253,12 +1256,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>The NBFC must compensate the borrower at the rate of ₹5,000 for each day of delay beyond 30 days in releasing original movable/immovable property documents, if the delay is attributable to the NBFC [1]. Additionally, if the delay is not attributable to the NBFC, the NBFC must communicate the reasons for the delay to the borrower [2]. The 30-day timeline for release is specified in F.1 [3].</t>
+          <t>The NBFC must compensate the borrower at the rate of ₹5,000 for each day of delay beyond 30 days in releasing original movable/immovable property documents, if the delay is attributable to the NBFC [1]. Additionally, if the delay pertains to pledged collateral, the compensation rate is also ₹5,000 per day of delay beyond the prescribed timeline [2].</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>12942_Responsible-Business-Conduct.pdf p.20 | 12942_Responsible-Business-Conduct.pdf p.24 | 12942_Responsible-Business-Conduct.pdf p.19 | 12957_Credit-Facilities.pdf p.15 | 12942_Responsible-Business-Conduct.pdf p.14 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.7</t>
+          <t>12942_Responsible-Business-Conduct.pdf p.20 | 12942_Responsible-Business-Conduct.pdf p.24 | 12942_Responsible-Business-Conduct.pdf p.19 | 12942_Responsible-Business-Conduct.pdf p.14 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.7 | 12943_Know-Your-Customer.pdf p.34</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1272,7 +1275,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -1306,26 +1309,26 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>The cap on default loss guarantee (DLG) cover in digital lending is five per cent of the total amount disbursed from the loan portfolio. This applies to NBFCs, including those engaged in digital lending, as specified in the regulations. For example, a DLG set of ₹40 crore would have a DLG cover ceiling of ₹2 crore (5% of ₹40 crore), which activates proportionally as loans are disbursed [1]. The cap is calculated based on disbursed amounts, not the total portfolio, and remains fixed for the DLG set [1]. No separate cap for digital lending is mentioned in the passages.</t>
+          <t>The cap on Default Loss Guarantee (DLG) cover is five per cent of the total amount disbursed from the loan portfolio, as specified in [1]. This applies generally to NBFCs and their loan portfolios, including those in digital lending, but the context passages do not explicitly mention a separate cap for digital lending. The DLG cover is calculated proportionally to disbursed amounts, as illustrated in [1] and [4]. No distinct cap for digital lending is stated in the provided texts.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>12957_Credit-Facilities.pdf p.24 | 12957_Credit-Facilities.pdf p.25 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.14 | 12957_Credit-Facilities.pdf p.26 | 12957_Credit-Facilities.pdf p.8 | 12952_Transfer-and-Distribution-of-Credit-Risk.pdf p.36</t>
+          <t>12957_Credit-Facilities.pdf p.24 | 12957_Credit-Facilities.pdf p.25 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.14 | 12957_Credit-Facilities.pdf p.26 | 12957_Credit-Facilities.pdf p.8 | 12957_Credit-Facilities.pdf p.6</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>all key figures present (5%)</t>
+          <t>none of the expected figures appear (5%)</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -1359,7 +1362,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>The minimum cooling-off period for digital loans is one day, as determined by the NBFC's credit policy, subject to the period not being less than one day [1].</t>
+          <t>The minimum cooling-off period for digital loans is one day, as stipulated in [1], which states that the cooling-off period shall not be less than one day.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1378,7 +1381,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -1413,9 +1416,9 @@
       <c r="F19" t="inlineStr">
         <is>
           <t>The credit concentration limits for a Middle Layer NBFC are:  
-- **25 per cent of its Tier 1 capital** to a single party; and  
-- **40 per cent of its Tier 1 capital** to a single group of parties [1].  
-These norms apply to NBFCs except NBFC-IFC and NBFC-UL (Upper Layer), as specified in the context [1].</t>
+- **25 per cent of its Tier 1 capital** to a single party;  
+- **40 per cent of its Tier 1 capital** to a single group of parties.  
+These limits may be exceeded by **5 per cent** for a single party and **10 per cent** for a single group if the additional exposure is for infrastructure loans or investments [1].</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1434,7 +1437,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>11</v>
+        <v>12.9</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1468,12 +1471,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NBFCs must report credit information to credit information companies **monthly** for wilful defaulters [1] and large defaulters [2]. For structured digital lending products, reporting is required "irrespective of its nature / tenor" under the same monthly framework [5]. Quarterly reporting applies only to specific credit risk transfer exposures [4].</t>
+          <t>NBFCs must report credit information to credit information companies **monthly** for wilful defaulters [1] and large defaulters [2]. Other reporting requirements, such as quarterly [4] or half-yearly [6], pertain to specific categories (e.g., credit risk exposure, relief measures) and are distinct from general credit information reporting.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>12946_Wilful-Defaulters-and-Large-Defaulters.pdf p.17 | 12946_Wilful-Defaulters-and-Large-Defaulters.pdf p.17 | 12952_Transfer-and-Distribution-of-Credit-Risk.pdf p.38 | 12954_Credit-Risk-Management.pdf p.22 | 12957_Credit-Facilities.pdf p.21 | 12946_Wilful-Defaulters-and-Large-Defaulters.pdf p.20</t>
+          <t>12946_Wilful-Defaulters-and-Large-Defaulters.pdf p.17 | 12946_Wilful-Defaulters-and-Large-Defaulters.pdf p.17 | 12952_Transfer-and-Distribution-of-Credit-Risk.pdf p.38 | 12954_Credit-Risk-Management.pdf p.22 | 12957_Credit-Facilities.pdf p.21 | 12947_Resolution-of-Stressed-Assets.pdf p.41</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1487,7 +1490,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1521,7 +1524,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>An NBFC identified in the Upper Layer must list its equity shares within three years of identification [1], [2].</t>
+          <t>An NBFC identified in the Upper Layer must get its equity shares listed within **three years** of identification [1], [2].</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1540,7 +1543,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1574,12 +1577,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>No, collection staff cannot call borrowers late at night. The guidelines specify that recovery agents must contact borrowers between 8:00 a.m. and 7:00 p.m. [3](6)(e), and persistently calling before 9:00 a.m. or after 6:00 p.m. is explicitly prohibited as a harsh recovery practice [2](91)(2). Additionally, borrowers may request to avoid calls at specific times, which must be honored [3](6)(f).</t>
+          <t>No, collection staff cannot call borrowers late at night. The NBFC and HFC guidelines explicitly prohibit contacting borrowers outside specific hours. For instance, recovery agents must contact customers between **8:00 a.m. to 7:00 p.m.** for overdue loans [3], and persistently calling before **8:00 a.m.** or after **7:00 p.m.** is deemed a harsh practice [2]. Additionally, NBFCs are instructed to avoid "undue harassment," including calls at "odd hours" [4]. These restrictions apply regardless of whether the borrower answers during the day.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>12942_Responsible-Business-Conduct.pdf p.28 | 12942_Responsible-Business-Conduct.pdf p.27 | 12939_Housing-Finance-Companies.pdf p.70 | 12942_Responsible-Business-Conduct.pdf p.9 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.28 | 12939_Housing-Finance-Companies.pdf p.72</t>
+          <t>12942_Responsible-Business-Conduct.pdf p.28 | 12942_Responsible-Business-Conduct.pdf p.27 | 12939_Housing-Finance-Companies.pdf p.70 | 12942_Responsible-Business-Conduct.pdf p.9 | 12939_Housing-Finance-Companies.pdf p.66 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.28</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1593,7 +1596,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -1627,13 +1630,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>If a borrower pays off the overdue interest but still owes some principal, the account cannot be upgraded from NPA to standard asset unless **entire arrears of interest and principal** are paid. Paragraph 24 explicitly states that NPAs may be upgraded to standard assets only upon full repayment of all arrears (interest and principal) [2]. Partial payments (e.g., paying overdue interest but leaving principal unpaid) do not satisfy this condition. 
-Additionally, paragraph 43 defines NPA based on overdue interest or principal exceeding 90/180 days, but upgradation requires resolution of **all** outstanding obligations [4]. Thus, residual principal would keep the account in NPA status.</t>
+          <t>No. According to paragraph 24, loan accounts classified as NPAs may be upgraded as 'standard' asset only if **entire arrears of interest and principal** are paid by the borrower. If the borrower pays off the overdue interest but still owes principal, the account remains in NPA status until all principal is repaid [24]. Similarly, paragraph 43 defines NPA to include assets where **interest or principal** remains overdue for more than 180 days [3]. Thus, partial repayment of interest without settling principal does not remove the account from NPA classification.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.8 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.7 | 12939_Housing-Finance-Companies.pdf p.21 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.17 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.20 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.12</t>
+          <t>12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.8 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.7 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.17 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.20 | 12947_Resolution-of-Stressed-Assets.pdf p.35 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.17</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1647,7 +1649,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>10.2</v>
+        <v>7.5</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1681,7 +1683,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>When rates go up, floating-rate borrowers are **not required** to switch to a fixed rate. The NBFC may, at its option, provide the choice to switch to a fixed rate as per its Board-approved policy [1]. However, this switch is optional, and borrowers are not mandatorily obligated to do so. The policy may specify the number of times a borrower can switch during the loan tenor [1]. Similarly, the policy on reset of floating rate personal loans explicitly includes the option to switch between fixed and floating rates but does not enforce it [2].</t>
+          <t>No, borrowers are not required to switch to a fixed rate when interest rates rise. The policy allows NBFCs to offer borrowers the option to switch from floating to fixed rates at their discretion, but this is not mandatory. The borrower may choose to switch or not, as specified in the NBFC's Board-approved policy [1], and this option is also referenced in the Fair Practices Code for lending [2]. The decision to switch remains optional for the borrower.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1700,7 +1702,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -1734,7 +1736,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>No, penal interest cannot be added when a customer pays late. Penal charges for non-compliance (e.g., late repayment) are distinct from penal interest and must be levied as 'penal charges' without capitalization (i.e., no further interest on such charges) [1][2]. However, normal interest on unpaid principal or unpaid EMI may still be charged at the contracted rate until remediation [1]. For credit cards, late payment charges are applied on the outstanding amount after the due date, but interest is only levied on the adjusted outstanding amount, not the total amount due [3].</t>
+          <t>No, penal interest cannot be added when a customer pays late. Penal charges for non-compliance, including late repayment, must be levied as separate penal charges and not as penal interest added to the interest rate. Interest may still be charged on unpaid interest (including unpaid EMI) at the contracted rate until remediation, but penal charges themselves are not capitalized or treated as part of the interest rate [1][2].</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1753,7 +1755,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -1787,7 +1789,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>No, the classification of an NBFC into the Upper Layer is determined by the Reserve Bank of India (RBI) based on scale-based regulatory parameters, not self-declared. Once identified as NBFC-UL (Upper Layer), the entity must comply with mandated timelines and regulatory requirements, including submitting a Board-approved roadmap for compliance with listed company standards [1][6]. The transition and categorization are governed by RBI's directives, not autonomous decisions by the NBFC.</t>
+          <t>No, the classification of an NBFC into the Upper Layer is determined by the Reserve Bank of India (RBI) based on scale-based regulatory parameters, not self-declared. Passage [1] states that NBFC-UL must be "identified" as such, and Passage [2][3] clarify that CICs/HFCs are included in layers depending on RBI-specified criteria. Additionally, Passage [4] mentions that NBFCs are "categorised" as NBFC-UL, and Passage [6] outlines RBI-advisory timelines for transition. Thus, the RBI, not the NBFC itself, decides layer classification [1][2][3][4][6].</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1806,7 +1808,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>4.8</v>
+        <v>7.3</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -1840,7 +1842,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>No, a foreclosure fee cannot be charged for prepaying a floating-rate personal loan to a salaried individual. According to paragraph 34(1) of the Reserve Bank of India (Non-Banking Financial Companies - Responsible Business Conduct) Directions, 2025, NBFCs shall not levy pre-payment charges on floating rate loans granted for purposes other than business to individuals [3]. Since the loan is for a personal purpose (salaried individual), this provision explicitly prohibits pre-payment charges, including foreclosure fees.</t>
+          <t>No, a foreclosure fee cannot be charged for prepaying a floating-rate personal loan for a salaried individual. According to [3] §34(1), NBFCs are prohibited from levying pre-payment charges on floating rate loans granted for purposes other than business to individuals. Additionally, [1] §163(1) explicitly states that pre-payment levies are not applicable for floating rate housing loans pre-closed from any source. Since the loan is floating-rate and the prepayment is initiated by the borrower (not the NBFC), no foreclosure charges are permissible.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1859,7 +1861,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -1893,12 +1895,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>The NBFC must ensure that loan disbursements are made directly into the borrower's bank account, except for specific statutory or regulatory cases [4]. Funds collected from borrowers (e.g., EMIs) must be transferred through escrow accounts operated by a bank trustee, with strict rules against using these accounts for unauthorized purposes [3]. The lending app partner, if acting as a Loan Servicing Provider (LSP), would handle collections via the escrow mechanism, not their own bank account. Thus, collecting EMIs into the app partner's own account would violate the prescribed funds transfer mechanism and disbursement rules.</t>
+          <t>The lending app partner cannot collect EMIs into its own bank account. According to [4], loan disbursements must be made into the borrower's bank account, and LSPs (Loan Servicing Providers) must not have control over the flow of funds. Additionally, [3] mandates that funds must be transferred through escrow accounts and bank accounts, prohibiting direct use of funds for repayment or disbursement. Thus, EMIs must be collected from the borrower's account and forwarded, with the LSP acting only as an intermediary without direct control over the funds.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>13586_SUP-Miscellaneous.pdf p.5 | 12942_Responsible-Business-Conduct.pdf p.16 | 12934_Peer-to-Peer-Lending-Platform.pdf p.11 | 12957_Credit-Facilities.pdf p.15 | 12939_Housing-Finance-Companies.pdf p.104 | 12952_Transfer-and-Distribution-of-Credit-Risk.pdf p.22</t>
+          <t>13586_SUP-Miscellaneous.pdf p.5 | 12942_Responsible-Business-Conduct.pdf p.16 | 12934_Peer-to-Peer-Lending-Platform.pdf p.11 | 12957_Credit-Facilities.pdf p.15 | 12939_Housing-Finance-Companies.pdf p.104 | 12952_Transfer-and-Distribution-of-Credit-Risk.pdf p.37</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1912,7 +1914,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -1946,7 +1948,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>The customer has 30 days to resolve a complaint before approaching the RBI Ombudsman. If the card-issuer does not respond within 30 days after filing the complaint or rejects it wholly/partly, the customer can escalate to the Ombudsman [1]. This timeline is also stipulated for NBFCs in cases where complaints are rejected or unresolved [3], and reiterated for digital lending grievances [6].</t>
+          <t>The customer has 30 days to resolve a complaint before approaching the RBI Ombudsman. If the card-issuer does not respond within 30 days after filing the complaint or rejects it wholly/partly, the customer can escalate to the Ombudsman [1]. This timeline is also reiterated in the context of NBFCs and their grievance redressal mechanisms [3], and explicitly stated as the period for seeking resolution before approaching the RBI Ombudsman [6].</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1965,7 +1967,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -1999,12 +2001,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>No, the NBFC shall not outsource the entire internal audit function. The Internal Audit function is explicitly prohibited from being outsourced, and ownership of audit reports must remain with regular functionaries of the Internal Audit function [1]. Core management functions, including internal audit, are also listed as activities that shall not be outsourced [3]. While external experts may be hired for specific tasks (e.g., IT/IS audit) under certain conditions, the entire function cannot be transferred to an outside firm.</t>
+          <t>No, the entire internal audit function cannot be outsourced. The NBFC shall not outsource the Internal Audit function [1], and core management functions including Internal Audit are explicitly listed as activities that shall not be outsourced [3]. While external experts may be hired on a contractual basis for specific tasks (e.g., IT/IS audit) if internal expertise is lacking, ownership of audit reports and responsibility for the function remain with the internal audit team [1][4].</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>13589_SUP-Internal-Audit-Function.pdf p.11 | 12941_Managing-Risks-in-Outsourcing.pdf p.13 | 12941_Managing-Risks-in-Outsourcing.pdf p.12 | 13592_SUP-Cybersecurity-Technology-Risk-Resilience.pdf p.23 | 12941_Managing-Risks-in-Outsourcing.pdf p.23 | 13588_SUP-Statutory-Audit.pdf p.11</t>
+          <t>13589_SUP-Internal-Audit-Function.pdf p.11 | 12941_Managing-Risks-in-Outsourcing.pdf p.13 | 12941_Managing-Risks-in-Outsourcing.pdf p.12 | 13592_SUP-Cybersecurity-Technology-Risk-Resilience.pdf p.23 | 13588_SUP-Statutory-Audit.pdf p.11 | 12952_Transfer-and-Distribution-of-Credit-Risk.pdf p.17</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2018,7 +2020,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -2052,7 +2054,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>The Compliance function must be headed by a Chief Compliance Officer (CCO) as per [1], which mandates the CCO to head the Compliance Department. However, the passages do not specify any requirement for annual rotation of the CCO or compliance heads. Rotation policies mentioned in the context apply to statutory auditors (e.g., audit firms cannot be reappointed in the same NBFC for six years after a term [3]), but no such rule is stated for compliance heads. Thus, while a separate compliance head is required, the context does not support the claim that they must be rotated annually.</t>
+          <t>The NBFC must appoint a compliance officer (CCO) as a senior executive reporting to the Board, responsible for statutory and legal compliance [4]. There is no requirement to rotate compliance heads annually; the passages only specify audit firm rotation every three years [2][3]. The CCO's role is permanent under the described structure.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2062,16 +2064,16 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>declined to answer an in-scope question - retrieval likely missed</t>
+          <t>no numeric facts to compare - read the answer yourself</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2105,7 +2107,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yes, loan terms must be explained in a language understood by the borrower. The Key Facts Statement (KFS) must be provided in a language understood by borrowers [1]. Loan agreements and terms must be conveyed in the vernacular language as understood by the borrower [2]. The Fair Practices Code (FPC) and loan agreements for microfinance loans must also be in a language understood by the borrower [3]. Notices regarding changes in terms and conditions must be in the vernacular language or a language as understood by the borrower [4]. All communications to the borrower, including terms and conditions, must be in the vernacular language or a language chosen by the borrower [5].</t>
+          <t>Yes, loan terms must be explained in a language the borrower understands. The Key Facts Statement (KFS) must be provided in a language understood by the borrower [1]. Loan agreements and terms must be conveyed in the vernacular language or a language as understood by the borrower [2]. The loan card, which includes terms and conditions, must also be in a language understood by the borrower [3]. Notices regarding changes in terms and conditions must be in the vernacular or a language the borrower understands [4]. All communications to the borrower, including terms and conditions, must be in the regional language or a language chosen by the borrower [5]. Additionally, important terms and conditions for illiterate borrowers must be explained in the presence of a witness, using the borrower's preferred language [6].</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2124,7 +2126,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -2158,7 +2160,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yes, before selling a repossessed vehicle, the borrower must be given a final chance to repay the loan. The terms and conditions of the loan agreement must include a provision ensuring this final opportunity for repayment before the sale/auction of the property [1]. Additionally, the notice period before taking possession of the security must be observed, which inherently involves warning the borrower [3]. These requirements are part of the legally enforceable clauses mandated for NBFCs and HFCs [1][4].</t>
+          <t>Yes, before selling a repossessed vehicle, the borrower must be given a final chance to repay the loan. The terms and conditions of the loan agreement must include a provision ensuring this final opportunity for repayment before the sale/auction of the property [1]. Additionally, a notice period is required before taking possession of the security, which is part of the legally enforceable re-possession clause [1]. These requirements are also reiterated in the context of HFCs' compliance with legal procedures for enforcing security interests [4].</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2177,7 +2179,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -2211,7 +2213,10 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>A depositor cannot request repayment of a public deposit within two months of investment, as premature repayment by an NBFC is generally restricted to cases where the depositor requests it **after three months** from the date of deposit [1]. Exceptions exist only for specific emergent circumstances, such as critical illness (allowing 100% repayment before three months) or "tiny deposits" (allowing full repayment for individual depositors in certain cases) [3]. Without such exceptions, repayment before three months is not permitted.</t>
+          <t>A depositor cannot generally receive their money back two months after investing, as premature repayment of public deposits by an NBFC not being a problem NBFC is only permitted **after the expiry of three months from the date of deposit** [1]. Exceptions exist for:  
+- **Tiny deposits** (entire amount repaid without interest before three months) [3], though "tiny deposits" are not quantified in the passage.  
+- **Critical illness** (100% repayment without interest before three months) [3].  
+Without meeting these specific exceptions, the NBFC must wait until the three-month period expires to repay the deposit.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2230,7 +2235,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -2264,7 +2269,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Yes, different interest rates can be charged to borrowers who seem similar, provided the differentiation is based on relevant factors such as risk profile, cost of funds, and other criteria outlined in the regulations. For instance, [1] mandates that NBFCs determine interest rates considering factors like cost of funds, margin, and risk premium, and disclose the rationale for different rates to different borrower categories. Similarly, [2] states that the blended interest rate is calculated based on the risk profile of the borrower and the proportionate funding share of respective REs under CLA. However, such differentiation must be transparent, with clear disclosure of the methodology and rationale, as required in [1] and [5]. Additionally, [3] specifies that penal charges (not interest rates) within the same product category must be uniform and non-discriminatory, but this does not preclude rate variations based on justified factors. Thus, while similar borrowers may have different rates if their risk profiles or other relevant factors differ, the practice must adhere to disclosure and transparency requirements.</t>
+          <t>Yes, NBFCs can charge different interest rates to borrowers who seem similar, provided the differentiation is based on justified factors and transparently disclosed. The interest rate model must account for factors like cost of funds, margin, and risk premium [1]. Additionally, the rationale for charging different rates to different categories of borrowers must be explicitly communicated in the sanction letter and disclosed on the NBFC's website [1]. For example, blended interest rates may vary based on the risk profile of borrowers and the proportionate funding share of respective REs under CLA [2]. However, penal charges within the same product category must be uniform and non-discriminatory, avoiding revenue enhancement [3]. Thus, differences in rates must be grounded in material factors and adhere to regulatory transparency requirements.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2283,7 +2288,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>12.8</v>
+        <v>9.6</v>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -2317,7 +2322,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yes, there is a cap. The NBFC must ensure that the outflows for repayment of monthly loan obligations of a household do not exceed **50 per cent of the monthly household income** [1]. This limit applies to all outstanding loans, including both principal and interest, and excludes future income from assets financed by the loan [1].</t>
+          <t>Yes, there is a cap. The NBFC must ensure that the outflows on account of repayment of monthly loan obligations of a household do not exceed **50 per cent of the monthly household income** [1]. This limit applies to all outstanding loans, including existing ones and the loan under consideration [1].</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2336,7 +2341,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>5.4</v>
+        <v>6.1</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -2370,17 +2375,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>The applicable provisions for a Middle Layer NBFC launching app-based personal loans through a service provider are:  
-- **Chapter III** of the Directions, which covers material outsourcing arrangements, including app-based services (e.g., loan processing, data handling) [1].  
-- **Chapter IV** and IT-specific provisions in **Chapter II** (e.g., Board-level IT outsourcing policy) [1].  
-- **Paragraphs 53–57** of the Directions, applicable to Middle Layer and above [4].  
-- **Provisions for NBFCs in Middle Layer** under the 2025 Regulatory Structure [1][2][4][6].  
-These apply because Middle Layer NBFCs are explicitly covered under these chapters and paragraphs, and the outsourcing of app-based personal loans falls under "material outsourcing arrangements" [1].</t>
+          <t>The provisions of the Directions applicable to Middle Layer NBFCs include:  
+- **Chapter IV** and **IT-specific provisions in Chapter II** (e.g., Board-level IT outsourcing policy) [1].  
+- **Paragraphs 6–19, 23–33, and 50–52** from the Directions [2], which apply to Middle Layer NBFCs.  
+- **Outsourcing arrangements** for financial services like loan processing (including app-based personal loans) are covered under Chapter III, subject to layer-wise applicability [1].  
+These apply to your Middle Layer NBFC’s app-based personal loans through a service provider.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>12941_Managing-Risks-in-Outsourcing.pdf p.4 | 12953_Concentration-Risk-Management.pdf p.2 | 12931_Miscellaneous.pdf p.2 | 12961_Undertaking-of-Financial-Services.pdf p.2 | 12946_Wilful-Defaulters-and-Large-Defaulters.pdf p.3 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.2</t>
+          <t>12941_Managing-Risks-in-Outsourcing.pdf p.4 | 12961_Undertaking-of-Financial-Services.pdf p.2 | 12946_Wilful-Defaulters-and-Large-Defaulters.pdf p.3 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.2 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.2 | 12950_Investment-Portfolio-Classification-Valuation.pdf p.3</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2394,7 +2398,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -2428,12 +2432,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>When your NBFC crosses ₹1,000 crore in asset size, it will transition from Base Layer (NBFC-BL) to Middle Layer (NBFC-ML) classification. This triggers compliance with regulatory requirements under paragraph 34 of the Directions, including stricter reporting and operational standards applicable to NBFC-ML [1]. Additionally, all non-deposit taking NBFCs attaining this threshold must adhere to extant NBFC-ML regulations, regardless of when the size is achieved [1]. If part of a group, consolidated assets exceeding ₹1,000 crore would also classify individual NBFCs in the group as NBFC-ML [2]. Note that temporary dips below ₹1,000 crore due to fluctuations do not exempt compliance with ML requirements until the next audited balance sheet is submitted [1].</t>
+          <t>When your NBFC crosses ₹1,000 crore in asset size, it will transition from Base Layer (BL) to Middle Layer (ML) classification [1][3]. This triggers compliance with ML regulatory requirements, including reporting obligations and frameworks applicable to NBFC-ML [1]. Additionally, audit standards will increase: for asset sizes above ₹1,000 crore, the NBFC must appoint auditors meeting stricter criteria (e.g., minimum 3 full-time partners, 2 FCA partners, 15 years of audit experience) compared to BL thresholds [6]. These changes apply once the asset size threshold is met, even if temporary fluctuations later reduce the size below ₹1,000 crore [1].</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.12 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.11 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13 | 12961_Undertaking-of-Financial-Services.pdf p.2 | 12947_Resolution-of-Stressed-Assets.pdf p.35</t>
+          <t>12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.12 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.11 | 12947_Resolution-of-Stressed-Assets.pdf p.15 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13 | 13588_SUP-Statutory-Audit.pdf p.8</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2447,7 +2451,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>10.1</v>
+        <v>10.9</v>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
@@ -2481,17 +2485,18 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>To start accepting public deposits, a non-deposit-taking Middle Layer NBFC must comply with the prudential norms and regulatory framework outlined in the Reserve Bank of India (Non-Banking Financial Companies - Acceptance of Public Deposits) Directions, 2025. Specifically:  
-1. **Eligibility**: The NBFC must meet the minimum net owned funds (NOF) requirements and comply with all prudential norms, including capital adequacy ratios and asset classification standards [4][6].  
-2. **Deposit Limits**: It may accept or renew public deposits up to **1.5 times its NOF**. Exceeding this limit would restrict renewal or acceptance of fresh deposits until compliance is achieved [6].  
-3. **Classification**: Transitioning from non-deposit-taking to deposit-taking status likely requires reclassification under the RBI’s scale-based regulation framework (e.g., from Type I NBFC to Type II NBFC or another category) [1][2].  
-4. **Reporting**: The NBFC must submit quarterly statements of capital funds, risk assets, and risk asset ratios (DNBS03) to the RBI [5].  
-**Conclusion**: Yes, a non-deposit-taking Middle Layer NBFC can start accepting public deposits **if it meets the NOF thresholds, prudential norms, and regulatory requirements**, and obtains necessary approvals from the RBI.</t>
+          <t>To start accepting public deposits, a non-deposit-taking Middle Layer NBFC must meet the following criteria:  
+1. **Minimum NOF Requirement**: The NBFC must have a minimum Net Owned Funds (NOF) as stipulated by the Reserve Bank [4].  
+2. **Prudential Norms**: It must comply with all prudential norms [4].  
+3. **Deposit Acceptance Limit**: Public deposits accepted or renewed, along with outstanding amounts, must not exceed one and one-half times its NOF [4].  
+4. **Application Form Compliance**: It must use the prescribed application form soliciting public deposits, including disclosures about credit ratings, dispute resolution mechanisms, and financial statements [6].  
+5. **Classification**: As a Middle Layer NBFC under the Scale Based Regulation (SBR) framework, it is subject to the applicable regulations for deposit-taking NBFCs [5].  
+If these conditions are met, the NBFC can transition to accepting public deposits. However, if it is classified as a **Type I NBFC** (not availing public funds and without customer interface), it cannot accept deposits [1].</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.7 | 13586_SUP-Miscellaneous.pdf p.2 | 12962_Branch-Authorisation.pdf p.4 | 12958_Acceptance-of-Public-Deposits.pdf p.2 | 13585_SUP-Auditors-Report.pdf p.6 | 12958_Acceptance-of-Public-Deposits.pdf p.13</t>
+          <t>12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.7 | 12962_Branch-Authorisation.pdf p.4 | 12958_Acceptance-of-Public-Deposits.pdf p.2 | 12958_Acceptance-of-Public-Deposits.pdf p.13 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.2 | 12958_Acceptance-of-Public-Deposits.pdf p.17</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2505,7 +2510,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>11.2</v>
+        <v>12.1</v>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
@@ -2539,26 +2544,26 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>The applicable LTV ratio for gold loans is determined by the NBFC's credit policy under the Reserve Bank of India (Non-Banking Financial Companies - Credit Facilities) Directions, 2025, as amended [5]. The exact percentage is not specified in the provided contexts, but the policy must include "appropriate single borrower limits and aggregate limits for the portfolio of loans against collateral of jewellery, ornaments or coins made of gold or silver" and define the maximum permissible LTV ratio [1]. For specific thresholds, reference to the Directions is required.</t>
+          <t>The LTV ratio for gold loans is determined by the NBFC's credit policy as per the Reserve Bank of India (Non-Banking Financial Companies - Credit Facilities) Directions, 2025, as amended [4]. The exact permissible maximum LTV ratio is not explicitly stated in the provided passages, but the policy must include it [1]. For loans against shares, a 50% LTV ratio is specified for NBFCs with assets of ₹100 crore and above [2], but this does not directly apply to gold loans. The NBFC must define the maximum LTV ratio in its policy, considering valuation standards and norms for gold and silver purity [1].</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>12957_Credit-Facilities.pdf p.29 | 12957_Credit-Facilities.pdf p.47 | 12957_Credit-Facilities.pdf p.1 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.10 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.11 | 12953_Concentration-Risk-Management.pdf p.2</t>
+          <t>12957_Credit-Facilities.pdf p.29 | 12957_Credit-Facilities.pdf p.47 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.10 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.11 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.10 | 12942_Responsible-Business-Conduct.pdf p.21</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>declined to answer an in-scope question - retrieval likely missed</t>
+          <t>found 2025; missing 75%, 85%, 2.5lakh, 2026</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>17.8</v>
+        <v>18.5</v>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
@@ -2593,16 +2598,13 @@
       <c r="F41" t="inlineStr">
         <is>
           <t>To ensure compliance when outsourcing collections to an agency, an NBFC must:  
-- Define terms and conditions in a legally binding written agreement, vetted by legal counsel, and include service standards, access to records, and monitoring mechanisms [1][3].  
-- Ensure the service provider maintains confidentiality controls, data security, and liability for breaches [1][3][4].  
-- Grant the NBFC rights to audit the service provider, access audit trails, and inspect its operations, including post-termination [1][2][3].  
-- Include provisions for subcontractor approval, business continuity plans, and contingency measures [1][3][61].  
-- Maintain data storage in India (if applicable) and ensure compliance with the Information Technology Act, 2000, and other legal requirements [3][4].  
-- Prohibit the service provider from being owned or controlled by NBFC directors or their relatives, unless approved by the Board [6].  
-- Report cyber incidents to the NBFC within six hours of detection, and ensure the NBFC reports them to the RBI within six hours [61].  
-- Ensure outsourcing does not impede RBI’s supervisory functions or compromise internal controls, reputation, or regulatory obligations [4].  
-- For offshore providers, verify jurisdictional compliance, data storage in India, and prevent unauthorized access to Indian operations by foreign regulators [5].  
-- Include post-termination obligations, such as preserving documents and maintaining customer confidentiality [1][3].</t>
+- Define terms and conditions in a written agreement, vetted by legal counsel, with provisions for service standards, access to books/records, continuous monitoring, subcontractor approval, confidentiality controls, and contingency plans [1].  
+- Ensure the service provider maintains data confidentiality, incorporates liability for security breaches, and preserves documents post-termination [1].  
+- Allow the NBFC to conduct audits of the service provider and grant RBI access to relevant records and information [1][2].  
+- Ensure data storage complies with Indian regulatory requirements (e.g., data stored only in India) and adherence to the Information Technology Act, 2000 [3].  
+- Prohibit the service provider from being owned or controlled by NBFC directors, key managerial personnel, or their relatives [4][6].  
+- Report cyber incidents to the NBFC within six hours of detection by the service provider, and ensure business continuity preparedness [2][61].  
+- Maintain post-termination confidentiality of customer information and ensure the service provider cooperates with regulators during insolvency or resolution [3][12].</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2621,7 +2623,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>12.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
@@ -2655,18 +2657,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>The Middle Layer NBFC must comply with core technology system requirements outlined in the context passages. Specifically:  
-- A **Board-approved IT/IS policy** is mandated, covering basic security aspects like physical/logical access controls, password policies, user roles, and maker-checker concepts [2].  
-- The IT strategy must ensure a **robust capacity management plan** to handle transaction volumes and customer growth, with periodic reviews of IT/IT security architecture and technology platforms [1].  
-- **Backup and testing** of data and applications are required at least **half-yearly** to ensure recovery without loss of transactions or audit trails [1].  
-- The **Early Warning Signals (EWS) framework** must be integrated with **Core Banking Solution (CBS)** or other operational systems for fraud risk management [6].  
-- **Periodic risk assessments** must evaluate technology stacks, third-party dependencies, and cybersecurity controls, with updates to the Risk and Control Self-Assessment (RCSA) as needed [1].  
-These requirements apply regardless of the number of branches, including 12 branches.</t>
+          <t>The Middle Layer NBFC must adhere to the following core technology system requirements:  
+- **Core Banking Solution (CBS) integration**: The Early Warning Signals (EWS) framework must be integrated with CBS or other operational systems [4].  
+- **Board-approved IT/IS policy**: The IT systems must include physical/logical access controls, password policies, user roles, maker-checker concepts, and robust cybersecurity controls [2].  
+- **Robust IT architecture**: The IT strategy must ensure capacity management plans to meet demand and periodic reviews of IT/IT security architecture [1].  
+- **Data backup and testing**: Periodic data backup with testing is mandated [2].  
+These requirements ensure cybersecurity, operational resilience, and compliance with governance frameworks.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>13591_SUP-Digital-Payment-Security-Controls.pdf p.8 | 13592_SUP-Cybersecurity-Technology-Risk-Resilience.pdf p.10 | 12957_Credit-Facilities.pdf p.15 | 13591_SUP-Digital-Payment-Security-Controls.pdf p.18 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.12 | 13590_SUP-Fraud-Risk-Management.pdf p.10</t>
+          <t>13591_SUP-Digital-Payment-Security-Controls.pdf p.8 | 13592_SUP-Cybersecurity-Technology-Risk-Resilience.pdf p.10 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.12 | 13590_SUP-Fraud-Risk-Management.pdf p.10 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.21 | 12931_Miscellaneous.pdf p.7</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2680,7 +2681,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -2714,7 +2715,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>No, a Middle Layer NBFC cannot levy pre-payment charges on floating rate term loans sanctioned for business purposes to micro and small enterprises (MSEs) with a sanctioned amount/limit up to ₹50 lakh [1](#1). This prohibition applies irrespective of the source of funds used for pre-payment and without a minimum lock-in period [1](#1).</t>
+          <t>Under the provisions for loans sanctioned on or after January 1, 2026, a Middle Layer NBFC cannot levy pre-payment charges on floating-rate term loans granted to micro and small enterprises (MSEs) with a sanctioned amount/limit up to ₹50 lakh [1][4]. This restriction applies irrespective of the pre-payment source and excludes retrospective charges [1]. For loans exceeding ₹50 lakh, pre-payment charges would depend on the NBFC's approved policy [1].</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2733,7 +2734,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -2767,19 +2768,21 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>The main new obligations for an NBFC identified as Upper Layer (NBFC-UL) include:  
-1. **Mandatory listing within three years** of identification [1][3].  
-2. **Board-approved roadmap** for compliance with listed company disclosure requirements under SEBI’s 2015 regulations, even before actual listing [1][3].  
-3. **Implementation plan** to adhere to enhanced regulatory framework within 24 months from the date of RBI classification advice [2].  
-4. **Submission of the roadmap** to the Reserve Bank for supervisory review [2].  
-5. **Subject to enhanced regulatory requirements** for at least five years post-classification, unless exiting via voluntary strategic adjustments [4].  
-6. Compliance with **concentration risk management norms** applicable to NBFC-ULs, including limits on large exposures (10% of eligible capital base) [5][6].  
-Government-owned NBFC-ULs are exempt from some provisions [1][5].</t>
+          <t>The main new obligations for an identified Upper Layer NBFC (NBFC-UL) are:  
+1. **Mandatory listing within three years** of identification, with disclosure requirements aligned to listed companies even before listing [1][3].  
+2. **Board composition** requiring a mix of educational qualifications and experience, with specific expertise based on business type [3].  
+3. **Transition plan**:  
+   - A Board-approved policy and implementation plan must be established within three months of classification [2].  
+   - Adherence to enhanced regulations must be achieved within 24 months from classification [2].  
+   - The implementation roadmap must be submitted to the Reserve Bank for supervisory review [2].  
+4. **Enhanced regulatory requirements** applicable for at least five years post-classification, unless the NBFC meets criteria to exit early via voluntary strategic adjustments (not due to adverse financial conditions) [4].  
+5. **Reporting obligations**: Independent Directors’ removal/resignation before completing their tenure must be reported to supervisors [3].  
+6. **Exemption**: Provisions do not apply to NBFC-ULs fully owned/controlled by the Government [1][3].</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>12945_Financial-Statements-Presentation-Disclosures.pdf p.47 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.14 | 12960_Governance.pdf p.17 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.15 | 12953_Concentration-Risk-Management.pdf p.2 | 12953_Concentration-Risk-Management.pdf p.6</t>
+          <t>12945_Financial-Statements-Presentation-Disclosures.pdf p.47 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.14 | 12960_Governance.pdf p.17 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.15 | 12943_Know-Your-Customer.pdf p.63 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.16</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2793,7 +2796,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -2827,12 +2830,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>The risk weight for unsecured consumer loans (classified as retail loans excluding housing loans, educational loans, vehicle loans, loans against gold jewellery, and microfinance/SHG loans) is 125% [4].</t>
+          <t>The risk weight for unsecured consumer loans (classified as retail loans, excluding housing loans, educational loans, vehicle loans, loans against gold jewellery, and microfinance/SHG loans) is **125%** [3]. This applies to NBFCs under the prudential norms for risk-weighted assets.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>12953_Concentration-Risk-Management.pdf p.10 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.22 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.44 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.22 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.26 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.21</t>
+          <t>12953_Concentration-Risk-Management.pdf p.10 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.22 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.22 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.26 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.53 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.52</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2846,7 +2849,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>6.4</v>
+        <v>9.5</v>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -2880,7 +2883,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>The ₹6 crore loan to a director's relative (a "related party") falls under the materiality threshold rules for Middle Layer NBFCs. According to [3], the materiality threshold for Middle Layer NBFCs is ₹5 crore. Since the loan exceeds this threshold, it must be sanctioned by the Board of the NBFC [3]. Additionally, the relative is classified as a "related party" under [5], which defines relatives of directors as included in the related party framework. The loan is also subject to credit risk management regulations applicable to Middle Layer NBFCs, as outlined in the Directions [2][4].</t>
+          <t>The ₹6 crore loan to a director's relative (a "related party") falls under the materiality threshold rules for Middle Layer NBFCs. According to [3], the materiality threshold for Middle Layer NBFCs is ₹5 crore. Since the loan exceeds this threshold, it must be sanctioned by the Board of the NBFC [3]. Additionally, the relative of a director is explicitly defined as a "related party" under [5], reinforcing the applicability of related party lending rules. No other specific exemptions or conditions apply here.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2933,20 +2936,20 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>- Co-lending arrangements must comply with the Reserve Bank of India (Non-Banking Financial Companies - Transfer and Distribution of Credit Risk) Directions, 2025 [1].  
-- No third party (other than lenders in the co-lending transaction) may have direct or indirect control over fund flows [1].  
-- The originating NBFC must transfer the loan share to the partner RE under CLA only as per the ex-ante agreement and KFS, within 15 calendar days of disbursement; otherwise, the loan remains on the originating NBFC’s books [2].  
-- NBFCs under CLA must retain a minimum 10% share of individual loans in their books [4].  
-- The CLA agreement must specify borrower selection criteria, product lines, fees, segregation of responsibilities, and grievance redressal mechanisms [4].  
-- Loans under CLA must be included in internal/statutory audits [2].  
-- NBFCs must ensure digital lending products, DLAs, and LSP details are publicly accessible on their websites [1].  
-- Disbursement must be directly into the borrower’s bank account, except for statutory mandates or co-lending (where funds must flow directly to the end-beneficiary) [1].  
-- Compliance with KYC norms and fair practice codes is mandatory [2].</t>
+          <t>The key rules for a Middle Layer NBFC entering co-lending with a bank are:  
+1. Co-lending arrangements must comply with the **Reserve Bank of India (Non-Banking Financial Companies - Transfer and Distribution of Credit Risk) Directions, 2025** [1].  
+2. **No third party** (other than the lenders in the co-lending transaction) shall have direct or indirect control over the flow of funds [1].  
+3. NBFCs under a **Credit Line Agreement (CLA)** must retain a **minimum 10% share** of individual loans in their books [3].  
+4. The CLA agreement must include **detailed terms** such as segregation of responsibilities, criteria for borrower selection, fees, and grievance redressal mechanisms [3].  
+5. Loan agreements must disclose **role segregation** (e.g., sourcing vs. servicing) and specify the **single point of contact** for the borrower [3].  
+6. Compliance with **prudential norms** (e.g., CRAR, NPA limits) and **accounting standards** for unrealized profit under CLAs is required [3].  
+7. **Digitally signed documents** (e.g., KFS, loan terms) must be automatically sent to borrowers via registered email/SMS upon contract execution [1].  
+8. **Disbursement** must be directly into the borrower’s bank account, except for statutory mandates or specific end-use cases [1].</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>12957_Credit-Facilities.pdf p.15 | 12952_Transfer-and-Distribution-of-Credit-Risk.pdf p.37 | 12961_Undertaking-of-Financial-Services.pdf p.13 | 12952_Transfer-and-Distribution-of-Credit-Risk.pdf p.35 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13 | 12946_Wilful-Defaulters-and-Large-Defaulters.pdf p.3</t>
+          <t>12957_Credit-Facilities.pdf p.15 | 12961_Undertaking-of-Financial-Services.pdf p.13 | 12952_Transfer-and-Distribution-of-Credit-Risk.pdf p.35 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13 | 12946_Wilful-Defaulters-and-Large-Defaulters.pdf p.3 | 12934_Peer-to-Peer-Lending-Platform.pdf p.11</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2960,7 +2963,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -2994,18 +2997,15 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>The conditions for onboarding customers via video KYC (V-CIP) include:  
-- Ensuring the customer’s photograph in Aadhaar/ODV matches the one during V-CIP, and identification details in Aadhaar/ODV and PAN/e-PAN align with the customer’s provided details [2].  
-- Conducting a concurrent audit to operationalize accounts opened via V-CIP [2].  
-- Storing V-CIP data and recordings in India, securely with timestamps for historical reference [2].  
-- Preserving activity logs of the V-CIP process with credentials of the official performing it [2].  
-- For new customers, verifying PAN details from the issuing authority during periodic KYC updates [1].  
-- Adhering to balance and credit limits: aggregate deposit balances ≤ ₹1 lakh, aggregate credits ≤ ₹2 lakh annually, and term loans ≤ ₹60,000 for borrowal accounts [3].  
-- Closing accounts if balances exceed thresholds without completing CDD [3].  
-- Ensuring periodic KYC updates follow risk-based approaches and internal policies approved by the Board [1].  
-- Avoiding accounts in fictitious names and applying CDD for all joint account holders [4].  
-- Verifying PAN, GST, and digital signatures as per statutory requirements [4].  
-- Not allowing other REs to use KYC data from OTP-based accounts without fresh authentication [3].</t>
+          <t>The conditions applicable to your Middle Layer NBFC onboarding customers via video KYC (V-CIP) are as follows:  
+1. **Verification of Identity**: The NBFC must ensure the customer’s photograph in Aadhaar/ODV matches the one during V-CIP, and the PAN details in Aadhaar/ODV must align with the customer’s provided details [2].  
+2. **Concurrent Audit**: Accounts opened via V-CIP must be operational only after a concurrent audit to ensure process integrity [2].  
+3. **Data Storage**: All V-CIP data and recordings must be stored in India, securely with timestamps for historical reference [2].  
+4. **Compliance with IT Act**: The NBFC must adhere to the Information Technology Act, 2000, for digital signatures and other statutory requirements [2].  
+5. **Conversion of Existing Accounts**: Existing accounts opened via Aadhaar OTP-based e-KYC may be converted to V-CIP, requiring full compliance with the V-CIP process [5].  
+6. **KYC Validity**: KYC verification by one branch is valid for account transfers within the same NBFC, provided full KYC is completed and not due for periodic updation [2].  
+7. **Document and Photo Matching**: During V-CIP, the NBFC must verify that the document’s information matches the customer’s live photo and entered details [2].  
+8. **Risk-Based Approach**: The NBFC must adopt a risk-based strategy for periodic KYC updates, specifying any exceptional measures in its internal policy [1].</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
@@ -3058,17 +3058,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>For a Middle Layer NBFC with over ₹1,000 crore in assets, the statutory auditor rules are as follows:  
-- **Audit Firm Requirements**: The NBFC must appoint audit firms meeting eligibility criteria based on its asset size. For asset sizes **above ₹1,000 crore and up to ₹15,000 crore**, the audit firm must have:  
-  - Minimum **3 full-time partners (FTPs)** with at least 3 years of association [6].  
-  - Minimum **2 Fellow Chartered Accountant (FCA) partners** among the FTPs [6].  
-  - Minimum **1 Full Time Partner/Paid CA with CISA/ISA qualification** [6].  
-  - Minimum **8 years of audit experience** for the firm [6].  
-  - Minimum **12 professional staff** [6].  
-- **Annual Certification**: Statutory auditors must certify the NBFC’s asset size (as of March 31) annually and submit it to the Reserve Bank’s Department of Supervision [3].  
-- **Branch Audit Coverage**: The NBFC must audit at least the top 20 branches (or top 20% of branches if fewer than 100) based on outstanding advances, covering a minimum of 15% of total gross advances [1].  
-- **Joint Audit**: If the NBFC’s asset size exceeds ₹15,000 crore, it must conduct statutory audits under joint audit by **minimum two audit firms** with no common partners or shared audit networks [1].  
-These rules apply to NBFCs in the Middle Layer category, which includes those with asset sizes of ₹1,000 crore or more [2].</t>
+          <t>For a Middle Layer NBFC with over ₹1,000 crore in assets:  
+- **Number of Statutory Auditors**: If the asset size is **above ₹15,000 crore**, the NBFC must conduct statutory audit under **joint audit by a minimum of two audit firms** [1]. For asset sizes **below ₹15,000 crore**, a **minimum of one audit firm** is required [1].  
+- **Joint Audit Requirements**: The NBFC must ensure joint auditors do not share common partners or belong to the same audit network (per Rule 6(3) of Companies (Audit and Auditors) Rules, 2014) [1].  
+- **Branch Coverage**: Auditors must cover **at least the top 20 branches** (or top 20% of branches if fewer than 100) based on outstanding advances, ensuring coverage of **minimum 15% of total gross advances** [1].  
+- **Eligibility Criteria for Auditors**: For asset sizes **above ₹15,000 crore**, the audit firm must have **minimum 5 full-time partners (FTPs)**, **4 FCA partners**, **2 CISA/ISA qualified staff**, **15 years of audit experience**, and **18 professional staff** [6]. For asset sizes **above ₹1,000 crore but up to ₹15,000 crore**, the requirements are **3 FTPs**, **2 FCA partners**, **1 CISA/ISA qualified staff**, **8 years of audit experience**, and **12 professional staff** [6].  
+- **Certification**: Statutory auditors must certify the NBFC’s asset size (as of March 31) annually and submit it to the Reserve Bank’s Department of Supervision [3].</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3087,7 +3082,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>17.3</v>
+        <v>26.7</v>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -3121,12 +3116,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>The borrower's 65-day overdue status classifies it as **SMA-2** (Special Mention Account-2), as per the criteria in paragraph 18 of [6], which defines SMA-2 as overdue between 60 and 90 days. This applies regardless of the NBFC's layer, as SMA classification is mandated for all loans [19]. Since 65 days falls within the SMA-2 range, it is not yet a non-performing asset (NPA), which requires overdue periods exceeding 90 days [1, 4].</t>
+          <t>The borrower is 65 days overdue, which falls within the SMA-2 category (more than 60 days and up to 90 days) as per paragraph 23 of context [5]. Since this is less than 90 days, it does not meet the NPA criteria for Middle Layer NBFCs [1], which require overdue periods exceeding 90 days. Thus, the classification is **SMA-2**.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.20 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.7 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.17 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.12 | 12947_Resolution-of-Stressed-Assets.pdf p.14</t>
+          <t>12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.20 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.7 | 12965_Registration-Exemptions-Scale-Based-Regulation.pdf p.13 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.17 | 12947_Resolution-of-Stressed-Assets.pdf p.14 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.5</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3140,7 +3135,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>19.1</v>
+        <v>14.5</v>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
@@ -3174,20 +3169,21 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>For a Middle Layer NBFC migrating its loan management system to a cloud vendor, the applicable provisions are:  
-- **Chapter III** of the Directions applies to material outsourcing arrangements, including cloud services [1]. This includes requirements for assessing business strategy, IT outsourcing policies, and risk management frameworks [3].  
-- **IT-specific provisions in Chapter II** (e.g., Board-level IT outsourcing policy) apply to Middle Layer NBFCs and above [1].  
-- **F.4 Usage of Cloud Computing Services** mandates specific controls, such as:  
-  - Comprehensive risk assessment of cloud adoption and data lifecycle management [3].  
-  - Cloud governance policies, including due diligence of CSPs, secure architecture, identity/access management (IAM), and integration with SOC [3-4].  
-  - Security controls aligned with NIST SP 800-210, encryption, data sovereignty, and multi-tenancy safeguards [3-4].  
-- **Exemptions**: NBFC-P2P, NBFC-AA, CICs, and NOFHCs are excluded [1][2][5].  
-These requirements ensure compliance with regulatory frameworks for cloud migration and outsourcing.</t>
+          <t>For a Middle Layer NBFC migrating its loan management system to a cloud vendor, the applicable provisions include:  
+- **Chapter IV** and **IT-specific provisions in Chapter II** of the Directions (applicable to Middle layer and above) [1].  
+- **F.4 Usage of Cloud Computing Services** (sections 96–110), which mandate:  
+  - Comprehensive assessment of cloud adoption aligning with business goals and risk [2].  
+  - IT outsourcing policies covering data lifecycle (generation to deletion) [2].  
+  - Risk management frameworks addressing multi-tenancy, data location, and security [2].  
+  - Cloud governance policies, including due diligence for CSPs, data sovereignty compliance, and integration with SOC [2][3].  
+  - Security controls per shared responsibility model, including IAM, encryption, and access management [3].  
+  - Monitoring requirements for CSPs, including testing, subcontractor assessments, and log retention [3].  
+These requirements ensure alignment with regulatory expectations for cloud migration in loan management systems.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>12941_Managing-Risks-in-Outsourcing.pdf p.4 | 12953_Concentration-Risk-Management.pdf p.2 | 12941_Managing-Risks-in-Outsourcing.pdf p.39 | 12941_Managing-Risks-in-Outsourcing.pdf p.41 | 12961_Undertaking-of-Financial-Services.pdf p.2 | 12957_Credit-Facilities.pdf p.15</t>
+          <t>12941_Managing-Risks-in-Outsourcing.pdf p.4 | 12941_Managing-Risks-in-Outsourcing.pdf p.39 | 12941_Managing-Risks-in-Outsourcing.pdf p.41 | 12957_Credit-Facilities.pdf p.15 | 12946_Wilful-Defaulters-and-Large-Defaulters.pdf p.3 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.2</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3201,7 +3197,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>9.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
@@ -3235,12 +3231,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>The provided context passages do not specify SEBI LODR disclosure timelines for listed NCDs. The references to SEBI LODR in the passages relate to corporate governance disclosures [2] and currency futures disclosures [5], but none address timelines for NCD-specific disclosures.</t>
+          <t>The provided context passages do not specify SEBI LODR disclosure timelines for listed NCDs. References to SEBI LODR in the context relate to corporate governance disclosures in annual reports [2] and currency futures disclosures [5], but none address timelines for NCD-specific disclosures.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>12938_Standalone-Primary-Dealers.pdf p.47 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.37 | 12947_Resolution-of-Stressed-Assets.pdf p.49 | 12931_Miscellaneous.pdf p.5 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.29 | 12939_Housing-Finance-Companies.pdf p.82</t>
+          <t>12938_Standalone-Primary-Dealers.pdf p.47 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.37 | 12947_Resolution-of-Stressed-Assets.pdf p.49 | 12931_Miscellaneous.pdf p.5 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.29 | 12938_Standalone-Primary-Dealers.pdf p.67</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3254,7 +3250,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
@@ -3288,12 +3284,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>The provided context passages do not specify SEBI's requirements for a debenture trustee in relation to public NCD issues.</t>
+          <t>The provided context passages do not specify SEBI's requirements for a debenture trustee in relation to public NCD issues. The discussions in the passages focus on regulatory frameworks for NCDs, including issuance limits, credit ratings, and compliance with RBI directions, but none directly address SEBI's mandates for debenture trustees.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>12938_Standalone-Primary-Dealers.pdf p.47 | 13585_SUP-Auditors-Report.pdf p.4 | 12931_Miscellaneous.pdf p.5 | 12938_Standalone-Primary-Dealers.pdf p.43 | 12943_Know-Your-Customer.pdf p.72 | 12947_Resolution-of-Stressed-Assets.pdf p.49</t>
+          <t>12938_Standalone-Primary-Dealers.pdf p.47 | 13585_SUP-Auditors-Report.pdf p.4 | 12931_Miscellaneous.pdf p.5 | 12938_Standalone-Primary-Dealers.pdf p.43 | 12947_Resolution-of-Stressed-Assets.pdf p.49 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.37</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3307,7 +3303,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>5.6</v>
+        <v>7.1</v>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
@@ -3341,7 +3337,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>The context passages do not specify a maximum number of insurers that an IRDAI corporate agent can tie up with. The relevant sections (e.g., [1][3][5]) outline conditions for acting as a corporate agent, such as obtaining IRDAI permission, avoiding restrictive practices, and ensuring voluntary customer choice, but none mention a numerical limit on the number of insurers. Thus, the answer cannot be determined from the provided passages.</t>
+          <t>The provided context passages do not specify a numerical limit on the number of insurers an IRDAI corporate agent can tie up with. The regulations mention requirements for obtaining permission, avoiding restrictive practices, and ensuring voluntary customer choices [1][3][5], but no explicit cap on the number of insurers is stated.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3360,7 +3356,7 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
@@ -3394,12 +3390,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>The provided context passages do not mention the TDS (Tax Deducted at Source) threshold on interest paid to depositors.</t>
+          <t>The provided context passages do not mention the TDS (Tax Deducted at Source) threshold on interest paid to depositors. No specific figure or rule related to TDS thresholds for interest payments is cited in the given documents.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>12958_Acceptance-of-Public-Deposits.pdf p.37 | 12949_Asset-Liability-Management.pdf p.40 | 12958_Acceptance-of-Public-Deposits.pdf p.14 | 12958_Acceptance-of-Public-Deposits.pdf p.20 | 12958_Acceptance-of-Public-Deposits.pdf p.4 | 12949_Asset-Liability-Management.pdf p.41</t>
+          <t>12958_Acceptance-of-Public-Deposits.pdf p.37 | 12949_Asset-Liability-Management.pdf p.40 | 12958_Acceptance-of-Public-Deposits.pdf p.14 | 12949_Asset-Liability-Management.pdf p.40 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.22 | 12949_Asset-Liability-Management.pdf p.41</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3413,7 +3409,7 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>5.1</v>
+        <v>7.5</v>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
@@ -3447,12 +3443,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>The context passages do not specify the exact GST rate applicable to loan processing fees. However, they mention that NBFCs must follow instructions from the Central Board of Indirect Taxes &amp; Customs (CBIC) regarding the applicability of GST on penal charges [1]. For loan processing fees, the GST treatment would depend on CBIC's clarifications, but no specific rate is provided in the given texts.</t>
+          <t>The context passages do not specify the exact GST rate applicable to loan processing fees. They only mention that NBFCs must follow instructions from the Central Board of Indirect Taxes &amp; Customs (CBIC) regarding the applicability of GST on penal charges [1]. No specific GST rate is provided in the text.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>12942_Responsible-Business-Conduct.pdf p.14 | 12939_Housing-Finance-Companies.pdf p.53 | 12956_Credit-Cards-Issuance-and-Conduct.pdf p.13 | 12942_Responsible-Business-Conduct.pdf p.4 | 12952_Transfer-and-Distribution-of-Credit-Risk.pdf p.36 | 12942_Responsible-Business-Conduct.pdf p.12</t>
+          <t>12942_Responsible-Business-Conduct.pdf p.14 | 12939_Housing-Finance-Companies.pdf p.53 | 12956_Credit-Cards-Issuance-and-Conduct.pdf p.13 | 12952_Transfer-and-Distribution-of-Credit-Risk.pdf p.36 | 12942_Responsible-Business-Conduct.pdf p.12 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.10</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3466,7 +3462,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
@@ -3500,12 +3496,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>The provided context passages do not mention any requirement to allocate 2% of profits to CSR (Corporate Social Responsibility). The content focuses on dividend payout ratios, capital adequacy norms, risk management, and regulatory definitions, but no reference to CSR obligations or profit allocation percentages is present.</t>
+          <t>The provided context passages do not mention any requirement to spend 2% of profits on CSR (Corporate Social Responsibility). The documents focus on regulatory guidelines for NBFCs, dividend payout ratios, capital adequacy, related party disclosures, and prudential norms, but none address CSR obligations or percentage allocations of profits to such purposes.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>12944_Declaration-of-Dividends.pdf p.6 | 12938_Standalone-Primary-Dealers.pdf p.3 | 12964_Acquisition-of-Shareholding-or-Control.pdf p.11 | 12953_Concentration-Risk-Management.pdf p.10 | 12947_Resolution-of-Stressed-Assets.pdf p.35 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.22</t>
+          <t>12944_Declaration-of-Dividends.pdf p.6 | 12938_Standalone-Primary-Dealers.pdf p.3 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.26 | 12953_Concentration-Risk-Management.pdf p.10 | 12947_Resolution-of-Stressed-Assets.pdf p.35 | 12932_Non-Operative-Financial-Holding-Companies.pdf p.10</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3519,7 +3515,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
@@ -3553,12 +3549,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>The context passages do not specify a deadline for holding the annual general meeting. They only mention that certain documents must be submitted to regulatory authorities within fifteen days of the meeting [1][2]. No explicit deadline for the meeting itself is provided in the text.</t>
+          <t>The context passages do not specify the deadline for holding an annual general meeting. They only mention that certain documents must be submitted within fifteen days of the meeting [1][2], but no explicit deadline for the meeting itself is provided.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>12939_Housing-Finance-Companies.pdf p.87 | 12958_Acceptance-of-Public-Deposits.pdf p.28 | 12955_Credit-Information-Reporting.pdf p.35 | 12947_Resolution-of-Stressed-Assets.pdf p.52 | 12949_Asset-Liability-Management.pdf p.36 | 12943_Know-Your-Customer.pdf p.41</t>
+          <t>12939_Housing-Finance-Companies.pdf p.87 | 12958_Acceptance-of-Public-Deposits.pdf p.28 | 12947_Resolution-of-Stressed-Assets.pdf p.52 | 13587_SUP-Supervisory-Returns.pdf p.11 | 12955_Credit-Information-Reporting.pdf p.60 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.27</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3572,7 +3568,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
@@ -3606,12 +3602,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>The provided context passages do not contain any information regarding trading windows for insiders or timelines related to results announcements.</t>
+          <t>The provided context passages do not contain information about trading windows for insiders or deadlines related to trading before results.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>12949_Asset-Liability-Management.pdf p.10 | 12938_Standalone-Primary-Dealers.pdf p.51 | 12938_Standalone-Primary-Dealers.pdf p.54 | 12949_Asset-Liability-Management.pdf p.38 | 12955_Credit-Information-Reporting.pdf p.32 | 12949_Asset-Liability-Management.pdf p.14</t>
+          <t>12938_Standalone-Primary-Dealers.pdf p.51 | 12949_Asset-Liability-Management.pdf p.14 | 12947_Resolution-of-Stressed-Assets.pdf p.52 | 12955_Credit-Information-Reporting.pdf p.35 | 13587_SUP-Supervisory-Returns.pdf p.9 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.25</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3625,7 +3621,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
@@ -3659,12 +3655,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>The provided context passages do not mention any commission rates or earnings related to group credit-life insurance sold with loans. The documents focus on regulatory definitions, data reporting requirements, and insurance business eligibility criteria for CICs, but none address financial commissions for such products.</t>
+          <t>The provided context passages do not contain information about commissions earned on group credit-life insurance sold with loans.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>12955_Credit-Information-Reporting.pdf p.55 | 12952_Transfer-and-Distribution-of-Credit-Risk.pdf p.6 | 12955_Credit-Information-Reporting.pdf p.65 | 12955_Credit-Information-Reporting.pdf p.62 | 12961_Undertaking-of-Financial-Services.pdf p.16 | 12955_Credit-Information-Reporting.pdf p.10</t>
+          <t>12955_Credit-Information-Reporting.pdf p.55 | 12955_Credit-Information-Reporting.pdf p.34 | 12956_Credit-Cards-Issuance-and-Conduct.pdf p.3 | 12939_Housing-Finance-Companies.pdf p.26 | 12935_Mortgage-Guarantee-Companies.pdf p.30 | 12959_Prudential-Norms-on-Capital-Adequacy.pdf p.25</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3678,7 +3674,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
@@ -3712,12 +3708,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>The provided context passages do not address tax deductibility of NPA provisions. They focus on accounting treatment, provisioning calculations, and asset classification rules under prudential norms, but do not mention tax implications or deductions related to NPAs.</t>
+          <t>The provided context passages do not address whether provisions for NPAs (Non-Performing Assets) are tax-deductible. The discussions focus on provisioning requirements, asset classification, and regulatory reporting standards, but none mention tax treatment or deductibility of NPA provisions.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.12 | 12949_Asset-Liability-Management.pdf p.29 | 12947_Resolution-of-Stressed-Assets.pdf p.57 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.44 | 12947_Resolution-of-Stressed-Assets.pdf p.35 | 12947_Resolution-of-Stressed-Assets.pdf p.15</t>
+          <t>12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.12 | 12949_Asset-Liability-Management.pdf p.29 | 12948_Income-Recognition-Asset-Classification-Provisioning.pdf p.10 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.44 | 12947_Resolution-of-Stressed-Assets.pdf p.35 | 12945_Financial-Statements-Presentation-Disclosures.pdf p.40</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3731,7 +3727,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
